--- a/plotting_and_statistics_script_with_demo_data/output_files_of_py_script/2024-06-11 02_15_01_1wire-temperatures.xlsx
+++ b/plotting_and_statistics_script_with_demo_data/output_files_of_py_script/2024-06-11 02_15_01_1wire-temperatures.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,42 +421,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Logger-id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date_time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Lumar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ImagerZ1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SZX12_R</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>M165FC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SZX12_L</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Axioplan2</t>
         </is>
@@ -480,7 +468,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>45443.69792824074</v>
       </c>
       <c r="C2" t="n">
@@ -508,7 +496,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>45443.70834490741</v>
       </c>
       <c r="C3" t="n">
@@ -536,7 +524,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>45443.71876157408</v>
       </c>
       <c r="C4" t="n">
@@ -564,7 +552,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>45443.72917824074</v>
       </c>
       <c r="C5" t="n">
@@ -592,7 +580,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>45443.73959490741</v>
       </c>
       <c r="C6" t="n">
@@ -620,7 +608,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>45443.75001157408</v>
       </c>
       <c r="C7" t="n">
@@ -648,7 +636,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>45443.76042824074</v>
       </c>
       <c r="C8" t="n">
@@ -676,7 +664,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="1" t="n">
         <v>45443.77084490741</v>
       </c>
       <c r="C9" t="n">
@@ -704,7 +692,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="1" t="n">
         <v>45443.78126157408</v>
       </c>
       <c r="C10" t="n">
@@ -732,7 +720,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="1" t="n">
         <v>45443.79167824074</v>
       </c>
       <c r="C11" t="n">
@@ -760,7 +748,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="1" t="n">
         <v>45443.80209490741</v>
       </c>
       <c r="C12" t="n">
@@ -788,7 +776,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="1" t="n">
         <v>45443.81251157408</v>
       </c>
       <c r="C13" t="n">
@@ -816,7 +804,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="1" t="n">
         <v>45443.82292824074</v>
       </c>
       <c r="C14" t="n">
@@ -844,7 +832,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="1" t="n">
         <v>45443.83334490741</v>
       </c>
       <c r="C15" t="n">
@@ -872,7 +860,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="1" t="n">
         <v>45443.84376157408</v>
       </c>
       <c r="C16" t="n">
@@ -900,7 +888,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="1" t="n">
         <v>45443.85417824074</v>
       </c>
       <c r="C17" t="n">
@@ -928,7 +916,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="1" t="n">
         <v>45443.86459490741</v>
       </c>
       <c r="C18" t="n">
@@ -956,7 +944,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="1" t="n">
         <v>45443.87501157408</v>
       </c>
       <c r="C19" t="n">
@@ -984,7 +972,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="1" t="n">
         <v>45443.88542824074</v>
       </c>
       <c r="C20" t="n">
@@ -1012,7 +1000,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="1" t="n">
         <v>45443.89584490741</v>
       </c>
       <c r="C21" t="n">
@@ -1040,7 +1028,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="1" t="n">
         <v>45443.90626157408</v>
       </c>
       <c r="C22" t="n">
@@ -1068,7 +1056,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="1" t="n">
         <v>45443.91667824074</v>
       </c>
       <c r="C23" t="n">
@@ -1096,7 +1084,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="1" t="n">
         <v>45443.92709490741</v>
       </c>
       <c r="C24" t="n">
@@ -1124,7 +1112,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="1" t="n">
         <v>45443.93751157408</v>
       </c>
       <c r="C25" t="n">
@@ -1152,7 +1140,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="1" t="n">
         <v>45443.94792824074</v>
       </c>
       <c r="C26" t="n">
@@ -1180,7 +1168,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="1" t="n">
         <v>45443.95834490741</v>
       </c>
       <c r="C27" t="n">
@@ -1208,7 +1196,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="1" t="n">
         <v>45443.96876157408</v>
       </c>
       <c r="C28" t="n">
@@ -1236,7 +1224,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="1" t="n">
         <v>45443.97917824074</v>
       </c>
       <c r="C29" t="n">
@@ -1264,7 +1252,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="1" t="n">
         <v>45443.98959490741</v>
       </c>
       <c r="C30" t="n">
@@ -1292,7 +1280,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="1" t="n">
         <v>45444.00001157408</v>
       </c>
       <c r="C31" t="n">
@@ -1320,7 +1308,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" s="1" t="n">
         <v>45444.01043981482</v>
       </c>
       <c r="C32" t="n">
@@ -1348,7 +1336,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" s="1" t="n">
         <v>45444.02085648148</v>
       </c>
       <c r="C33" t="n">
@@ -1376,7 +1364,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" s="1" t="n">
         <v>45444.03127314815</v>
       </c>
       <c r="C34" t="n">
@@ -1404,7 +1392,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" s="1" t="n">
         <v>45444.04168981482</v>
       </c>
       <c r="C35" t="n">
@@ -1432,7 +1420,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" s="1" t="n">
         <v>45444.05210648148</v>
       </c>
       <c r="C36" t="n">
@@ -1460,7 +1448,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" s="1" t="n">
         <v>45444.06252314815</v>
       </c>
       <c r="C37" t="n">
@@ -1488,7 +1476,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" s="1" t="n">
         <v>45444.07292824074</v>
       </c>
       <c r="C38" t="n">
@@ -1516,7 +1504,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" s="1" t="n">
         <v>45444.08334490741</v>
       </c>
       <c r="C39" t="n">
@@ -1544,7 +1532,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" s="1" t="n">
         <v>45444.09376157408</v>
       </c>
       <c r="C40" t="n">
@@ -1572,7 +1560,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="1" t="n">
         <v>45444.10418981482</v>
       </c>
       <c r="C41" t="n">
@@ -1600,7 +1588,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" s="1" t="n">
         <v>45444.11460648148</v>
       </c>
       <c r="C42" t="n">
@@ -1628,7 +1616,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" s="1" t="n">
         <v>45444.12501157408</v>
       </c>
       <c r="C43" t="n">
@@ -1656,7 +1644,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" s="1" t="n">
         <v>45444.13542824074</v>
       </c>
       <c r="C44" t="n">
@@ -1684,7 +1672,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" s="1" t="n">
         <v>45444.14584490741</v>
       </c>
       <c r="C45" t="n">
@@ -1712,7 +1700,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" s="1" t="n">
         <v>45444.15626157408</v>
       </c>
       <c r="C46" t="n">
@@ -1740,7 +1728,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" s="1" t="n">
         <v>45444.16668981482</v>
       </c>
       <c r="C47" t="n">
@@ -1768,7 +1756,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" s="1" t="n">
         <v>45444.17709490741</v>
       </c>
       <c r="C48" t="n">
@@ -1796,7 +1784,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="1" t="n">
         <v>45444.18751157408</v>
       </c>
       <c r="C49" t="n">
@@ -1824,7 +1812,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" s="1" t="n">
         <v>45444.19792824074</v>
       </c>
       <c r="C50" t="n">
@@ -1852,7 +1840,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="1" t="n">
         <v>45444.20834490741</v>
       </c>
       <c r="C51" t="n">
@@ -1880,7 +1868,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="1" t="n">
         <v>45444.21876157408</v>
       </c>
       <c r="C52" t="n">
@@ -1908,7 +1896,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" s="1" t="n">
         <v>45444.22917824074</v>
       </c>
       <c r="C53" t="n">
@@ -1936,7 +1924,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="1" t="n">
         <v>45444.23959490741</v>
       </c>
       <c r="C54" t="n">
@@ -1964,7 +1952,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="1" t="n">
         <v>45444.25001157408</v>
       </c>
       <c r="C55" t="n">
@@ -1992,7 +1980,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="1" t="n">
         <v>45444.26042824074</v>
       </c>
       <c r="C56" t="n">
@@ -2020,7 +2008,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" s="1" t="n">
         <v>45444.27084490741</v>
       </c>
       <c r="C57" t="n">
@@ -2048,7 +2036,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="1" t="n">
         <v>45444.28126157408</v>
       </c>
       <c r="C58" t="n">
@@ -2076,7 +2064,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="1" t="n">
         <v>45444.29167824074</v>
       </c>
       <c r="C59" t="n">
@@ -2104,7 +2092,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="1" t="n">
         <v>45444.30209490741</v>
       </c>
       <c r="C60" t="n">
@@ -2132,7 +2120,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" s="1" t="n">
         <v>45444.31251157408</v>
       </c>
       <c r="C61" t="n">
@@ -2160,7 +2148,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="1" t="n">
         <v>45444.32292824074</v>
       </c>
       <c r="C62" t="n">
@@ -2188,7 +2176,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="1" t="n">
         <v>45444.33334490741</v>
       </c>
       <c r="C63" t="n">
@@ -2216,7 +2204,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" s="1" t="n">
         <v>45444.34376157408</v>
       </c>
       <c r="C64" t="n">
@@ -2244,7 +2232,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="1" t="n">
         <v>45444.35417824074</v>
       </c>
       <c r="C65" t="n">
@@ -2272,7 +2260,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="1" t="n">
         <v>45444.36459490741</v>
       </c>
       <c r="C66" t="n">
@@ -2300,7 +2288,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" s="1" t="n">
         <v>45444.37501157408</v>
       </c>
       <c r="C67" t="n">
@@ -2328,7 +2316,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" s="1" t="n">
         <v>45444.38542824074</v>
       </c>
       <c r="C68" t="n">
@@ -2356,7 +2344,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="1" t="n">
         <v>45444.39584490741</v>
       </c>
       <c r="C69" t="n">
@@ -2384,7 +2372,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" s="1" t="n">
         <v>45444.40626157408</v>
       </c>
       <c r="C70" t="n">
@@ -2412,7 +2400,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" s="1" t="n">
         <v>45444.41667824074</v>
       </c>
       <c r="C71" t="n">
@@ -2440,7 +2428,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" s="1" t="n">
         <v>45444.42709490741</v>
       </c>
       <c r="C72" t="n">
@@ -2468,7 +2456,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" s="1" t="n">
         <v>45444.43751157408</v>
       </c>
       <c r="C73" t="n">
@@ -2496,7 +2484,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" s="1" t="n">
         <v>45444.44792824074</v>
       </c>
       <c r="C74" t="n">
@@ -2524,7 +2512,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" s="1" t="n">
         <v>45444.45834490741</v>
       </c>
       <c r="C75" t="n">
@@ -2552,7 +2540,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" s="1" t="n">
         <v>45444.46876157408</v>
       </c>
       <c r="C76" t="n">
@@ -2580,7 +2568,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" s="1" t="n">
         <v>45444.47917824074</v>
       </c>
       <c r="C77" t="n">
@@ -2608,7 +2596,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" s="1" t="n">
         <v>45444.48959490741</v>
       </c>
       <c r="C78" t="n">
@@ -2636,7 +2624,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" s="1" t="n">
         <v>45444.50001157408</v>
       </c>
       <c r="C79" t="n">
@@ -2664,7 +2652,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" s="1" t="n">
         <v>45444.51043981482</v>
       </c>
       <c r="C80" t="n">
@@ -2692,7 +2680,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" s="1" t="n">
         <v>45444.52085648148</v>
       </c>
       <c r="C81" t="n">
@@ -2720,7 +2708,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="1" t="n">
         <v>45444.53127314815</v>
       </c>
       <c r="C82" t="n">
@@ -2748,7 +2736,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" s="1" t="n">
         <v>45444.54168981482</v>
       </c>
       <c r="C83" t="n">
@@ -2776,7 +2764,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" s="1" t="n">
         <v>45444.55209490741</v>
       </c>
       <c r="C84" t="n">
@@ -2804,7 +2792,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" s="1" t="n">
         <v>45444.56252314815</v>
       </c>
       <c r="C85" t="n">
@@ -2832,7 +2820,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" s="1" t="n">
         <v>45444.57292824074</v>
       </c>
       <c r="C86" t="n">
@@ -2860,7 +2848,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" s="1" t="n">
         <v>45444.58334490741</v>
       </c>
       <c r="C87" t="n">
@@ -2888,7 +2876,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" s="1" t="n">
         <v>45444.59377314815</v>
       </c>
       <c r="C88" t="n">
@@ -2916,7 +2904,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" s="1" t="n">
         <v>45444.60418981482</v>
       </c>
       <c r="C89" t="n">
@@ -2944,7 +2932,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" s="1" t="n">
         <v>45444.61460648148</v>
       </c>
       <c r="C90" t="n">
@@ -2972,7 +2960,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" s="1" t="n">
         <v>45444.62501157408</v>
       </c>
       <c r="C91" t="n">
@@ -3000,7 +2988,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" s="1" t="n">
         <v>45444.63542824074</v>
       </c>
       <c r="C92" t="n">
@@ -3028,7 +3016,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="1" t="n">
         <v>45444.64584490741</v>
       </c>
       <c r="C93" t="n">
@@ -3056,7 +3044,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" s="1" t="n">
         <v>45444.65627314815</v>
       </c>
       <c r="C94" t="n">
@@ -3084,7 +3072,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" s="1" t="n">
         <v>45444.66668981482</v>
       </c>
       <c r="C95" t="n">
@@ -3112,7 +3100,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" s="1" t="n">
         <v>45444.67710648148</v>
       </c>
       <c r="C96" t="n">
@@ -3140,7 +3128,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" s="1" t="n">
         <v>45444.68752314815</v>
       </c>
       <c r="C97" t="n">
@@ -3168,7 +3156,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" s="1" t="n">
         <v>45444.69792824074</v>
       </c>
       <c r="C98" t="n">
@@ -3196,7 +3184,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" s="1" t="n">
         <v>45444.70834490741</v>
       </c>
       <c r="C99" t="n">
@@ -3224,7 +3212,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" s="1" t="n">
         <v>45444.71877314815</v>
       </c>
       <c r="C100" t="n">
@@ -3252,7 +3240,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" s="1" t="n">
         <v>45444.72917824074</v>
       </c>
       <c r="C101" t="n">
@@ -3280,7 +3268,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" s="1" t="n">
         <v>45444.73959490741</v>
       </c>
       <c r="C102" t="n">
@@ -3308,7 +3296,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n">
+      <c r="B103" s="1" t="n">
         <v>45444.75002314815</v>
       </c>
       <c r="C103" t="n">
@@ -3336,7 +3324,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n">
+      <c r="B104" s="1" t="n">
         <v>45444.76042824074</v>
       </c>
       <c r="C104" t="n">
@@ -3364,7 +3352,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" s="1" t="n">
         <v>45444.77085648148</v>
       </c>
       <c r="C105" t="n">
@@ -3392,7 +3380,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" s="1" t="n">
         <v>45444.78126157408</v>
       </c>
       <c r="C106" t="n">
@@ -3420,7 +3408,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n">
+      <c r="B107" s="1" t="n">
         <v>45444.79167824074</v>
       </c>
       <c r="C107" t="n">
@@ -3448,7 +3436,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" s="1" t="n">
         <v>45444.80210648148</v>
       </c>
       <c r="C108" t="n">
@@ -3476,7 +3464,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" s="1" t="n">
         <v>45444.81252314815</v>
       </c>
       <c r="C109" t="n">
@@ -3504,7 +3492,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" s="1" t="n">
         <v>45444.82293981482</v>
       </c>
       <c r="C110" t="n">
@@ -3532,7 +3520,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" s="1" t="n">
         <v>45444.83334490741</v>
       </c>
       <c r="C111" t="n">
@@ -3560,7 +3548,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n">
+      <c r="B112" s="1" t="n">
         <v>45444.84376157408</v>
       </c>
       <c r="C112" t="n">
@@ -3588,7 +3576,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B113" s="2" t="n">
+      <c r="B113" s="1" t="n">
         <v>45444.85417824074</v>
       </c>
       <c r="C113" t="n">
@@ -3616,7 +3604,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" s="1" t="n">
         <v>45444.86460648148</v>
       </c>
       <c r="C114" t="n">
@@ -3644,7 +3632,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" s="1" t="n">
         <v>45444.87502314815</v>
       </c>
       <c r="C115" t="n">
@@ -3672,7 +3660,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" s="1" t="n">
         <v>45444.88542824074</v>
       </c>
       <c r="C116" t="n">
@@ -3700,7 +3688,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n">
+      <c r="B117" s="1" t="n">
         <v>45444.89584490741</v>
       </c>
       <c r="C117" t="n">
@@ -3728,7 +3716,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" s="1" t="n">
         <v>45444.90626157408</v>
       </c>
       <c r="C118" t="n">
@@ -3756,7 +3744,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n">
+      <c r="B119" s="1" t="n">
         <v>45444.91667824074</v>
       </c>
       <c r="C119" t="n">
@@ -3784,7 +3772,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B120" s="2" t="n">
+      <c r="B120" s="1" t="n">
         <v>45444.92710648148</v>
       </c>
       <c r="C120" t="n">
@@ -3812,7 +3800,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B121" s="2" t="n">
+      <c r="B121" s="1" t="n">
         <v>45444.93752314815</v>
       </c>
       <c r="C121" t="n">
@@ -3840,7 +3828,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B122" s="2" t="n">
+      <c r="B122" s="1" t="n">
         <v>45444.94792824074</v>
       </c>
       <c r="C122" t="n">
@@ -3868,7 +3856,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B123" s="2" t="n">
+      <c r="B123" s="1" t="n">
         <v>45444.95834490741</v>
       </c>
       <c r="C123" t="n">
@@ -3896,7 +3884,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B124" s="2" t="n">
+      <c r="B124" s="1" t="n">
         <v>45444.96876157408</v>
       </c>
       <c r="C124" t="n">
@@ -3924,7 +3912,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B125" s="2" t="n">
+      <c r="B125" s="1" t="n">
         <v>45444.97917824074</v>
       </c>
       <c r="C125" t="n">
@@ -3952,7 +3940,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" s="1" t="n">
         <v>45444.98960648148</v>
       </c>
       <c r="C126" t="n">
@@ -3980,7 +3968,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B127" s="2" t="n">
+      <c r="B127" s="1" t="n">
         <v>45445.00001157408</v>
       </c>
       <c r="C127" t="n">
@@ -4008,7 +3996,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n">
+      <c r="B128" s="1" t="n">
         <v>45445.01043981482</v>
       </c>
       <c r="C128" t="n">
@@ -4036,7 +4024,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B129" s="2" t="n">
+      <c r="B129" s="1" t="n">
         <v>45445.02085648148</v>
       </c>
       <c r="C129" t="n">
@@ -4064,7 +4052,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" s="1" t="n">
         <v>45445.03127314815</v>
       </c>
       <c r="C130" t="n">
@@ -4092,7 +4080,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" s="1" t="n">
         <v>45445.04168981482</v>
       </c>
       <c r="C131" t="n">
@@ -4120,7 +4108,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B132" s="2" t="n">
+      <c r="B132" s="1" t="n">
         <v>45445.05209490741</v>
       </c>
       <c r="C132" t="n">
@@ -4148,7 +4136,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n">
+      <c r="B133" s="1" t="n">
         <v>45445.06251157408</v>
       </c>
       <c r="C133" t="n">
@@ -4176,7 +4164,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" s="1" t="n">
         <v>45445.07292824074</v>
       </c>
       <c r="C134" t="n">
@@ -4204,7 +4192,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B135" s="2" t="n">
+      <c r="B135" s="1" t="n">
         <v>45445.08335648148</v>
       </c>
       <c r="C135" t="n">
@@ -4232,7 +4220,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n">
+      <c r="B136" s="1" t="n">
         <v>45445.09377314815</v>
       </c>
       <c r="C136" t="n">
@@ -4260,7 +4248,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" s="1" t="n">
         <v>45445.10418981482</v>
       </c>
       <c r="C137" t="n">
@@ -4288,7 +4276,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n">
+      <c r="B138" s="1" t="n">
         <v>45445.11460648148</v>
       </c>
       <c r="C138" t="n">
@@ -4316,7 +4304,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B139" s="2" t="n">
+      <c r="B139" s="1" t="n">
         <v>45445.12501157408</v>
       </c>
       <c r="C139" t="n">
@@ -4344,7 +4332,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B140" s="2" t="n">
+      <c r="B140" s="1" t="n">
         <v>45445.13542824074</v>
       </c>
       <c r="C140" t="n">
@@ -4372,7 +4360,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B141" s="2" t="n">
+      <c r="B141" s="1" t="n">
         <v>45445.14584490741</v>
       </c>
       <c r="C141" t="n">
@@ -4400,7 +4388,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B142" s="2" t="n">
+      <c r="B142" s="1" t="n">
         <v>45445.15627314815</v>
       </c>
       <c r="C142" t="n">
@@ -4428,7 +4416,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B143" s="2" t="n">
+      <c r="B143" s="1" t="n">
         <v>45445.16668981482</v>
       </c>
       <c r="C143" t="n">
@@ -4456,7 +4444,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B144" s="2" t="n">
+      <c r="B144" s="1" t="n">
         <v>45445.17709490741</v>
       </c>
       <c r="C144" t="n">
@@ -4484,7 +4472,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B145" s="2" t="n">
+      <c r="B145" s="1" t="n">
         <v>45445.18752314815</v>
       </c>
       <c r="C145" t="n">
@@ -4512,7 +4500,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B146" s="2" t="n">
+      <c r="B146" s="1" t="n">
         <v>45445.19793981482</v>
       </c>
       <c r="C146" t="n">
@@ -4540,7 +4528,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B147" s="2" t="n">
+      <c r="B147" s="1" t="n">
         <v>45445.20834490741</v>
       </c>
       <c r="C147" t="n">
@@ -4568,7 +4556,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B148" s="2" t="n">
+      <c r="B148" s="1" t="n">
         <v>45445.21876157408</v>
       </c>
       <c r="C148" t="n">
@@ -4596,7 +4584,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B149" s="2" t="n">
+      <c r="B149" s="1" t="n">
         <v>45445.22917824074</v>
       </c>
       <c r="C149" t="n">
@@ -4624,7 +4612,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B150" s="2" t="n">
+      <c r="B150" s="1" t="n">
         <v>45445.23959490741</v>
       </c>
       <c r="C150" t="n">
@@ -4652,7 +4640,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B151" s="2" t="n">
+      <c r="B151" s="1" t="n">
         <v>45445.25002314815</v>
       </c>
       <c r="C151" t="n">
@@ -4680,7 +4668,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n">
+      <c r="B152" s="1" t="n">
         <v>45445.26043981482</v>
       </c>
       <c r="C152" t="n">
@@ -4708,7 +4696,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n">
+      <c r="B153" s="1" t="n">
         <v>45445.27085648148</v>
       </c>
       <c r="C153" t="n">
@@ -4736,7 +4724,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B154" s="2" t="n">
+      <c r="B154" s="1" t="n">
         <v>45445.28127314815</v>
       </c>
       <c r="C154" t="n">
@@ -4764,7 +4752,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B155" s="2" t="n">
+      <c r="B155" s="1" t="n">
         <v>45445.29167824074</v>
       </c>
       <c r="C155" t="n">
@@ -4792,7 +4780,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B156" s="2" t="n">
+      <c r="B156" s="1" t="n">
         <v>45445.30209490741</v>
       </c>
       <c r="C156" t="n">
@@ -4820,7 +4808,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B157" s="2" t="n">
+      <c r="B157" s="1" t="n">
         <v>45445.31251157408</v>
       </c>
       <c r="C157" t="n">
@@ -4848,7 +4836,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n">
+      <c r="B158" s="1" t="n">
         <v>45445.32292824074</v>
       </c>
       <c r="C158" t="n">
@@ -4876,7 +4864,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B159" s="2" t="n">
+      <c r="B159" s="1" t="n">
         <v>45445.33335648148</v>
       </c>
       <c r="C159" t="n">
@@ -4904,7 +4892,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B160" s="2" t="n">
+      <c r="B160" s="1" t="n">
         <v>45445.34376157408</v>
       </c>
       <c r="C160" t="n">
@@ -4932,7 +4920,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B161" s="2" t="n">
+      <c r="B161" s="1" t="n">
         <v>45445.35417824074</v>
       </c>
       <c r="C161" t="n">
@@ -4960,7 +4948,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B162" s="2" t="n">
+      <c r="B162" s="1" t="n">
         <v>45445.36459490741</v>
       </c>
       <c r="C162" t="n">
@@ -4988,7 +4976,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B163" s="2" t="n">
+      <c r="B163" s="1" t="n">
         <v>45445.37501157408</v>
       </c>
       <c r="C163" t="n">
@@ -5016,7 +5004,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B164" s="2" t="n">
+      <c r="B164" s="1" t="n">
         <v>45445.38543981482</v>
       </c>
       <c r="C164" t="n">
@@ -5044,7 +5032,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B165" s="2" t="n">
+      <c r="B165" s="1" t="n">
         <v>45445.39584490741</v>
       </c>
       <c r="C165" t="n">
@@ -5072,7 +5060,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B166" s="2" t="n">
+      <c r="B166" s="1" t="n">
         <v>45445.40627314815</v>
       </c>
       <c r="C166" t="n">
@@ -5100,7 +5088,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B167" s="2" t="n">
+      <c r="B167" s="1" t="n">
         <v>45445.41668981482</v>
       </c>
       <c r="C167" t="n">
@@ -5128,7 +5116,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B168" s="2" t="n">
+      <c r="B168" s="1" t="n">
         <v>45445.42710648148</v>
       </c>
       <c r="C168" t="n">
@@ -5156,7 +5144,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n">
+      <c r="B169" s="1" t="n">
         <v>45445.43751157408</v>
       </c>
       <c r="C169" t="n">
@@ -5184,7 +5172,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B170" s="2" t="n">
+      <c r="B170" s="1" t="n">
         <v>45445.44792824074</v>
       </c>
       <c r="C170" t="n">
@@ -5212,7 +5200,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B171" s="2" t="n">
+      <c r="B171" s="1" t="n">
         <v>45445.45834490741</v>
       </c>
       <c r="C171" t="n">
@@ -5240,7 +5228,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B172" s="2" t="n">
+      <c r="B172" s="1" t="n">
         <v>45445.46876157408</v>
       </c>
       <c r="C172" t="n">
@@ -5268,7 +5256,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B173" s="2" t="n">
+      <c r="B173" s="1" t="n">
         <v>45445.47917824074</v>
       </c>
       <c r="C173" t="n">
@@ -5296,7 +5284,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B174" s="2" t="n">
+      <c r="B174" s="1" t="n">
         <v>45445.48959490741</v>
       </c>
       <c r="C174" t="n">
@@ -5324,7 +5312,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B175" s="2" t="n">
+      <c r="B175" s="1" t="n">
         <v>45445.50002314815</v>
       </c>
       <c r="C175" t="n">
@@ -5352,7 +5340,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B176" s="2" t="n">
+      <c r="B176" s="1" t="n">
         <v>45445.51043981482</v>
       </c>
       <c r="C176" t="n">
@@ -5380,7 +5368,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B177" s="2" t="n">
+      <c r="B177" s="1" t="n">
         <v>45445.52084490741</v>
       </c>
       <c r="C177" t="n">
@@ -5408,7 +5396,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B178" s="2" t="n">
+      <c r="B178" s="1" t="n">
         <v>45445.53126157408</v>
       </c>
       <c r="C178" t="n">
@@ -5436,7 +5424,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B179" s="2" t="n">
+      <c r="B179" s="1" t="n">
         <v>45445.54167824074</v>
       </c>
       <c r="C179" t="n">
@@ -5464,7 +5452,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B180" s="2" t="n">
+      <c r="B180" s="1" t="n">
         <v>45445.55209490741</v>
       </c>
       <c r="C180" t="n">
@@ -5492,7 +5480,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B181" s="2" t="n">
+      <c r="B181" s="1" t="n">
         <v>45445.56251157408</v>
       </c>
       <c r="C181" t="n">
@@ -5520,7 +5508,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B182" s="2" t="n">
+      <c r="B182" s="1" t="n">
         <v>45445.57293981482</v>
       </c>
       <c r="C182" t="n">
@@ -5548,7 +5536,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B183" s="2" t="n">
+      <c r="B183" s="1" t="n">
         <v>45445.58335648148</v>
       </c>
       <c r="C183" t="n">
@@ -5576,7 +5564,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B184" s="2" t="n">
+      <c r="B184" s="1" t="n">
         <v>45445.59376157408</v>
       </c>
       <c r="C184" t="n">
@@ -5604,7 +5592,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B185" s="2" t="n">
+      <c r="B185" s="1" t="n">
         <v>45445.60417824074</v>
       </c>
       <c r="C185" t="n">
@@ -5632,7 +5620,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B186" s="2" t="n">
+      <c r="B186" s="1" t="n">
         <v>45445.61459490741</v>
       </c>
       <c r="C186" t="n">
@@ -5660,7 +5648,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B187" s="2" t="n">
+      <c r="B187" s="1" t="n">
         <v>45445.62502314815</v>
       </c>
       <c r="C187" t="n">
@@ -5688,7 +5676,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B188" s="2" t="n">
+      <c r="B188" s="1" t="n">
         <v>45445.63543981482</v>
       </c>
       <c r="C188" t="n">
@@ -5716,7 +5704,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B189" s="2" t="n">
+      <c r="B189" s="1" t="n">
         <v>45445.64585648148</v>
       </c>
       <c r="C189" t="n">
@@ -5744,7 +5732,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B190" s="2" t="n">
+      <c r="B190" s="1" t="n">
         <v>45445.65627314815</v>
       </c>
       <c r="C190" t="n">
@@ -5772,7 +5760,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B191" s="2" t="n">
+      <c r="B191" s="1" t="n">
         <v>45445.66667824074</v>
       </c>
       <c r="C191" t="n">
@@ -5800,7 +5788,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B192" s="2" t="n">
+      <c r="B192" s="1" t="n">
         <v>45445.67709490741</v>
       </c>
       <c r="C192" t="n">
@@ -5828,7 +5816,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B193" s="2" t="n">
+      <c r="B193" s="1" t="n">
         <v>45445.68751157408</v>
       </c>
       <c r="C193" t="n">
@@ -5856,7 +5844,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B194" s="2" t="n">
+      <c r="B194" s="1" t="n">
         <v>45445.69792824074</v>
       </c>
       <c r="C194" t="n">
@@ -5884,7 +5872,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B195" s="2" t="n">
+      <c r="B195" s="1" t="n">
         <v>45445.70834490741</v>
       </c>
       <c r="C195" t="n">
@@ -5912,7 +5900,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B196" s="2" t="n">
+      <c r="B196" s="1" t="n">
         <v>45445.71876157408</v>
       </c>
       <c r="C196" t="n">
@@ -5940,7 +5928,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B197" s="2" t="n">
+      <c r="B197" s="1" t="n">
         <v>45445.72917824074</v>
       </c>
       <c r="C197" t="n">
@@ -5968,7 +5956,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B198" s="2" t="n">
+      <c r="B198" s="1" t="n">
         <v>45445.73959490741</v>
       </c>
       <c r="C198" t="n">
@@ -5996,7 +5984,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B199" s="2" t="n">
+      <c r="B199" s="1" t="n">
         <v>45445.75001157408</v>
       </c>
       <c r="C199" t="n">
@@ -6024,7 +6012,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B200" s="2" t="n">
+      <c r="B200" s="1" t="n">
         <v>45445.76042824074</v>
       </c>
       <c r="C200" t="n">
@@ -6052,7 +6040,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B201" s="2" t="n">
+      <c r="B201" s="1" t="n">
         <v>45445.77084490741</v>
       </c>
       <c r="C201" t="n">
@@ -6080,7 +6068,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B202" s="2" t="n">
+      <c r="B202" s="1" t="n">
         <v>45445.78126157408</v>
       </c>
       <c r="C202" t="n">
@@ -6108,7 +6096,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B203" s="2" t="n">
+      <c r="B203" s="1" t="n">
         <v>45445.79167824074</v>
       </c>
       <c r="C203" t="n">
@@ -6136,7 +6124,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B204" s="2" t="n">
+      <c r="B204" s="1" t="n">
         <v>45445.80209490741</v>
       </c>
       <c r="C204" t="n">
@@ -6164,7 +6152,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B205" s="2" t="n">
+      <c r="B205" s="1" t="n">
         <v>45445.81251157408</v>
       </c>
       <c r="C205" t="n">
@@ -6192,7 +6180,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B206" s="2" t="n">
+      <c r="B206" s="1" t="n">
         <v>45445.82292824074</v>
       </c>
       <c r="C206" t="n">
@@ -6220,7 +6208,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B207" s="2" t="n">
+      <c r="B207" s="1" t="n">
         <v>45445.83334490741</v>
       </c>
       <c r="C207" t="n">
@@ -6248,7 +6236,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B208" s="2" t="n">
+      <c r="B208" s="1" t="n">
         <v>45445.84376157408</v>
       </c>
       <c r="C208" t="n">
@@ -6276,7 +6264,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B209" s="2" t="n">
+      <c r="B209" s="1" t="n">
         <v>45445.85417824074</v>
       </c>
       <c r="C209" t="n">
@@ -6304,7 +6292,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B210" s="2" t="n">
+      <c r="B210" s="1" t="n">
         <v>45445.86459490741</v>
       </c>
       <c r="C210" t="n">
@@ -6332,7 +6320,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B211" s="2" t="n">
+      <c r="B211" s="1" t="n">
         <v>45445.87501157408</v>
       </c>
       <c r="C211" t="n">
@@ -6360,7 +6348,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B212" s="2" t="n">
+      <c r="B212" s="1" t="n">
         <v>45445.88542824074</v>
       </c>
       <c r="C212" t="n">
@@ -6388,7 +6376,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B213" s="2" t="n">
+      <c r="B213" s="1" t="n">
         <v>45445.89584490741</v>
       </c>
       <c r="C213" t="n">
@@ -6416,7 +6404,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B214" s="2" t="n">
+      <c r="B214" s="1" t="n">
         <v>45445.90626157408</v>
       </c>
       <c r="C214" t="n">
@@ -6444,7 +6432,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B215" s="2" t="n">
+      <c r="B215" s="1" t="n">
         <v>45445.91667824074</v>
       </c>
       <c r="C215" t="n">
@@ -6472,7 +6460,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B216" s="2" t="n">
+      <c r="B216" s="1" t="n">
         <v>45445.92709490741</v>
       </c>
       <c r="C216" t="n">
@@ -6500,7 +6488,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B217" s="2" t="n">
+      <c r="B217" s="1" t="n">
         <v>45445.93751157408</v>
       </c>
       <c r="C217" t="n">
@@ -6528,7 +6516,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B218" s="2" t="n">
+      <c r="B218" s="1" t="n">
         <v>45445.94792824074</v>
       </c>
       <c r="C218" t="n">
@@ -6556,7 +6544,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B219" s="2" t="n">
+      <c r="B219" s="1" t="n">
         <v>45445.95834490741</v>
       </c>
       <c r="C219" t="n">
@@ -6584,7 +6572,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B220" s="2" t="n">
+      <c r="B220" s="1" t="n">
         <v>45445.96876157408</v>
       </c>
       <c r="C220" t="n">
@@ -6612,7 +6600,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B221" s="2" t="n">
+      <c r="B221" s="1" t="n">
         <v>45445.97917824074</v>
       </c>
       <c r="C221" t="n">
@@ -6640,7 +6628,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B222" s="2" t="n">
+      <c r="B222" s="1" t="n">
         <v>45445.98960648148</v>
       </c>
       <c r="C222" t="n">
@@ -6668,7 +6656,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B223" s="2" t="n">
+      <c r="B223" s="1" t="n">
         <v>45446.00001157408</v>
       </c>
       <c r="C223" t="n">
@@ -6696,7 +6684,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B224" s="2" t="n">
+      <c r="B224" s="1" t="n">
         <v>45446.01042824074</v>
       </c>
       <c r="C224" t="n">
@@ -6724,7 +6712,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B225" s="2" t="n">
+      <c r="B225" s="1" t="n">
         <v>45446.02084490741</v>
       </c>
       <c r="C225" t="n">
@@ -6752,7 +6740,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B226" s="2" t="n">
+      <c r="B226" s="1" t="n">
         <v>45446.03126157408</v>
       </c>
       <c r="C226" t="n">
@@ -6780,7 +6768,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B227" s="2" t="n">
+      <c r="B227" s="1" t="n">
         <v>45446.04168981482</v>
       </c>
       <c r="C227" t="n">
@@ -6808,7 +6796,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B228" s="2" t="n">
+      <c r="B228" s="1" t="n">
         <v>45446.05209490741</v>
       </c>
       <c r="C228" t="n">
@@ -6836,7 +6824,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B229" s="2" t="n">
+      <c r="B229" s="1" t="n">
         <v>45446.06252314815</v>
       </c>
       <c r="C229" t="n">
@@ -6864,7 +6852,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B230" s="2" t="n">
+      <c r="B230" s="1" t="n">
         <v>45446.07293981482</v>
       </c>
       <c r="C230" t="n">
@@ -6892,7 +6880,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B231" s="2" t="n">
+      <c r="B231" s="1" t="n">
         <v>45446.08334490741</v>
       </c>
       <c r="C231" t="n">
@@ -6920,7 +6908,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B232" s="2" t="n">
+      <c r="B232" s="1" t="n">
         <v>45446.09376157408</v>
       </c>
       <c r="C232" t="n">
@@ -6948,7 +6936,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B233" s="2" t="n">
+      <c r="B233" s="1" t="n">
         <v>45446.10417824074</v>
       </c>
       <c r="C233" t="n">
@@ -6976,7 +6964,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B234" s="2" t="n">
+      <c r="B234" s="1" t="n">
         <v>45446.11459490741</v>
       </c>
       <c r="C234" t="n">
@@ -7004,7 +6992,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B235" s="2" t="n">
+      <c r="B235" s="1" t="n">
         <v>45446.12502314815</v>
       </c>
       <c r="C235" t="n">
@@ -7032,7 +7020,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B236" s="2" t="n">
+      <c r="B236" s="1" t="n">
         <v>45446.13543981482</v>
       </c>
       <c r="C236" t="n">
@@ -7060,7 +7048,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B237" s="2" t="n">
+      <c r="B237" s="1" t="n">
         <v>45446.14585648148</v>
       </c>
       <c r="C237" t="n">
@@ -7088,7 +7076,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B238" s="2" t="n">
+      <c r="B238" s="1" t="n">
         <v>45446.15627314815</v>
       </c>
       <c r="C238" t="n">
@@ -7116,7 +7104,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B239" s="2" t="n">
+      <c r="B239" s="1" t="n">
         <v>45446.16668981482</v>
       </c>
       <c r="C239" t="n">
@@ -7144,7 +7132,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B240" s="2" t="n">
+      <c r="B240" s="1" t="n">
         <v>45446.17709490741</v>
       </c>
       <c r="C240" t="n">
@@ -7172,7 +7160,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B241" s="2" t="n">
+      <c r="B241" s="1" t="n">
         <v>45446.18751157408</v>
       </c>
       <c r="C241" t="n">
@@ -7200,7 +7188,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B242" s="2" t="n">
+      <c r="B242" s="1" t="n">
         <v>45446.19792824074</v>
       </c>
       <c r="C242" t="n">
@@ -7228,7 +7216,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B243" s="2" t="n">
+      <c r="B243" s="1" t="n">
         <v>45446.20834490741</v>
       </c>
       <c r="C243" t="n">
@@ -7256,7 +7244,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B244" s="2" t="n">
+      <c r="B244" s="1" t="n">
         <v>45446.21876157408</v>
       </c>
       <c r="C244" t="n">
@@ -7284,7 +7272,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B245" s="2" t="n">
+      <c r="B245" s="1" t="n">
         <v>45446.22917824074</v>
       </c>
       <c r="C245" t="n">
@@ -7312,7 +7300,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B246" s="2" t="n">
+      <c r="B246" s="1" t="n">
         <v>45446.23959490741</v>
       </c>
       <c r="C246" t="n">
@@ -7340,7 +7328,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B247" s="2" t="n">
+      <c r="B247" s="1" t="n">
         <v>45446.25001157408</v>
       </c>
       <c r="C247" t="n">
@@ -7368,7 +7356,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B248" s="2" t="n">
+      <c r="B248" s="1" t="n">
         <v>45446.26042824074</v>
       </c>
       <c r="C248" t="n">
@@ -7396,7 +7384,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B249" s="2" t="n">
+      <c r="B249" s="1" t="n">
         <v>45446.27084490741</v>
       </c>
       <c r="C249" t="n">
@@ -7424,7 +7412,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B250" s="2" t="n">
+      <c r="B250" s="1" t="n">
         <v>45446.28126157408</v>
       </c>
       <c r="C250" t="n">
@@ -7452,7 +7440,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B251" s="2" t="n">
+      <c r="B251" s="1" t="n">
         <v>45446.29167824074</v>
       </c>
       <c r="C251" t="n">
@@ -7480,7 +7468,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B252" s="2" t="n">
+      <c r="B252" s="1" t="n">
         <v>45446.30209490741</v>
       </c>
       <c r="C252" t="n">
@@ -7508,7 +7496,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B253" s="2" t="n">
+      <c r="B253" s="1" t="n">
         <v>45446.31251157408</v>
       </c>
       <c r="C253" t="n">
@@ -7536,7 +7524,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B254" s="2" t="n">
+      <c r="B254" s="1" t="n">
         <v>45446.32292824074</v>
       </c>
       <c r="C254" t="n">
@@ -7564,7 +7552,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B255" s="2" t="n">
+      <c r="B255" s="1" t="n">
         <v>45446.33334490741</v>
       </c>
       <c r="C255" t="n">
@@ -7592,7 +7580,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B256" s="2" t="n">
+      <c r="B256" s="1" t="n">
         <v>45446.34376157408</v>
       </c>
       <c r="C256" t="n">
@@ -7620,7 +7608,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B257" s="2" t="n">
+      <c r="B257" s="1" t="n">
         <v>45446.35417824074</v>
       </c>
       <c r="C257" t="n">
@@ -7648,7 +7636,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B258" s="2" t="n">
+      <c r="B258" s="1" t="n">
         <v>45446.36459490741</v>
       </c>
       <c r="C258" t="n">
@@ -7676,7 +7664,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B259" s="2" t="n">
+      <c r="B259" s="1" t="n">
         <v>45446.37501157408</v>
       </c>
       <c r="C259" t="n">
@@ -7704,7 +7692,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B260" s="2" t="n">
+      <c r="B260" s="1" t="n">
         <v>45446.38542824074</v>
       </c>
       <c r="C260" t="n">
@@ -7732,7 +7720,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B261" s="2" t="n">
+      <c r="B261" s="1" t="n">
         <v>45446.39584490741</v>
       </c>
       <c r="C261" t="n">
@@ -7760,7 +7748,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B262" s="2" t="n">
+      <c r="B262" s="1" t="n">
         <v>45446.40626157408</v>
       </c>
       <c r="C262" t="n">
@@ -7788,7 +7776,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B263" s="2" t="n">
+      <c r="B263" s="1" t="n">
         <v>45446.41667824074</v>
       </c>
       <c r="C263" t="n">
@@ -7816,7 +7804,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B264" s="2" t="n">
+      <c r="B264" s="1" t="n">
         <v>45446.42709490741</v>
       </c>
       <c r="C264" t="n">
@@ -7844,7 +7832,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B265" s="2" t="n">
+      <c r="B265" s="1" t="n">
         <v>45446.43751157408</v>
       </c>
       <c r="C265" t="n">
@@ -7872,7 +7860,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B266" s="2" t="n">
+      <c r="B266" s="1" t="n">
         <v>45446.44792824074</v>
       </c>
       <c r="C266" t="n">
@@ -7900,7 +7888,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B267" s="2" t="n">
+      <c r="B267" s="1" t="n">
         <v>45446.45834490741</v>
       </c>
       <c r="C267" t="n">
@@ -7928,7 +7916,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B268" s="2" t="n">
+      <c r="B268" s="1" t="n">
         <v>45446.46877314815</v>
       </c>
       <c r="C268" t="n">
@@ -7956,7 +7944,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B269" s="2" t="n">
+      <c r="B269" s="1" t="n">
         <v>45446.47918981482</v>
       </c>
       <c r="C269" t="n">
@@ -7984,7 +7972,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B270" s="2" t="n">
+      <c r="B270" s="1" t="n">
         <v>45446.48960648148</v>
       </c>
       <c r="C270" t="n">
@@ -8012,7 +8000,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B271" s="2" t="n">
+      <c r="B271" s="1" t="n">
         <v>45446.50001157408</v>
       </c>
       <c r="C271" t="n">
@@ -8040,7 +8028,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B272" s="2" t="n">
+      <c r="B272" s="1" t="n">
         <v>45446.51042824074</v>
       </c>
       <c r="C272" t="n">
@@ -8068,7 +8056,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B273" s="2" t="n">
+      <c r="B273" s="1" t="n">
         <v>45446.52084490741</v>
       </c>
       <c r="C273" t="n">
@@ -8096,7 +8084,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B274" s="2" t="n">
+      <c r="B274" s="1" t="n">
         <v>45446.53126157408</v>
       </c>
       <c r="C274" t="n">
@@ -8124,7 +8112,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B275" s="2" t="n">
+      <c r="B275" s="1" t="n">
         <v>45446.54168981482</v>
       </c>
       <c r="C275" t="n">
@@ -8152,7 +8140,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B276" s="2" t="n">
+      <c r="B276" s="1" t="n">
         <v>45446.55210648148</v>
       </c>
       <c r="C276" t="n">
@@ -8180,7 +8168,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B277" s="2" t="n">
+      <c r="B277" s="1" t="n">
         <v>45446.56252314815</v>
       </c>
       <c r="C277" t="n">
@@ -8208,7 +8196,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B278" s="2" t="n">
+      <c r="B278" s="1" t="n">
         <v>45446.57292824074</v>
       </c>
       <c r="C278" t="n">
@@ -8236,7 +8224,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B279" s="2" t="n">
+      <c r="B279" s="1" t="n">
         <v>45446.58334490741</v>
       </c>
       <c r="C279" t="n">
@@ -8264,7 +8252,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B280" s="2" t="n">
+      <c r="B280" s="1" t="n">
         <v>45446.59376157408</v>
       </c>
       <c r="C280" t="n">
@@ -8292,7 +8280,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B281" s="2" t="n">
+      <c r="B281" s="1" t="n">
         <v>45446.60417824074</v>
       </c>
       <c r="C281" t="n">
@@ -8320,7 +8308,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B282" s="2" t="n">
+      <c r="B282" s="1" t="n">
         <v>45446.61459490741</v>
       </c>
       <c r="C282" t="n">
@@ -8348,7 +8336,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B283" s="2" t="n">
+      <c r="B283" s="1" t="n">
         <v>45446.62501157408</v>
       </c>
       <c r="C283" t="n">
@@ -8376,7 +8364,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B284" s="2" t="n">
+      <c r="B284" s="1" t="n">
         <v>45446.63543981482</v>
       </c>
       <c r="C284" t="n">
@@ -8404,7 +8392,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B285" s="2" t="n">
+      <c r="B285" s="1" t="n">
         <v>45446.64585648148</v>
       </c>
       <c r="C285" t="n">
@@ -8432,7 +8420,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B286" s="2" t="n">
+      <c r="B286" s="1" t="n">
         <v>45446.65627314815</v>
       </c>
       <c r="C286" t="n">
@@ -8460,7 +8448,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B287" s="2" t="n">
+      <c r="B287" s="1" t="n">
         <v>45446.66667824074</v>
       </c>
       <c r="C287" t="n">
@@ -8488,7 +8476,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B288" s="2" t="n">
+      <c r="B288" s="1" t="n">
         <v>45446.67709490741</v>
       </c>
       <c r="C288" t="n">
@@ -8516,7 +8504,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B289" s="2" t="n">
+      <c r="B289" s="1" t="n">
         <v>45446.68751157408</v>
       </c>
       <c r="C289" t="n">
@@ -8544,7 +8532,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B290" s="2" t="n">
+      <c r="B290" s="1" t="n">
         <v>45446.69792824074</v>
       </c>
       <c r="C290" t="n">
@@ -8572,7 +8560,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B291" s="2" t="n">
+      <c r="B291" s="1" t="n">
         <v>45446.70834490741</v>
       </c>
       <c r="C291" t="n">
@@ -8600,7 +8588,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B292" s="2" t="n">
+      <c r="B292" s="1" t="n">
         <v>45446.71877314815</v>
       </c>
       <c r="C292" t="n">
@@ -8628,7 +8616,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B293" s="2" t="n">
+      <c r="B293" s="1" t="n">
         <v>45446.72918981482</v>
       </c>
       <c r="C293" t="n">
@@ -8656,7 +8644,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B294" s="2" t="n">
+      <c r="B294" s="1" t="n">
         <v>45446.73959490741</v>
       </c>
       <c r="C294" t="n">
@@ -8684,7 +8672,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B295" s="2" t="n">
+      <c r="B295" s="1" t="n">
         <v>45446.75001157408</v>
       </c>
       <c r="C295" t="n">
@@ -8712,7 +8700,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B296" s="2" t="n">
+      <c r="B296" s="1" t="n">
         <v>45446.76042824074</v>
       </c>
       <c r="C296" t="n">
@@ -8740,7 +8728,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B297" s="2" t="n">
+      <c r="B297" s="1" t="n">
         <v>45446.77084490741</v>
       </c>
       <c r="C297" t="n">
@@ -8768,7 +8756,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B298" s="2" t="n">
+      <c r="B298" s="1" t="n">
         <v>45446.78126157408</v>
       </c>
       <c r="C298" t="n">
@@ -8796,7 +8784,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B299" s="2" t="n">
+      <c r="B299" s="1" t="n">
         <v>45446.79168981482</v>
       </c>
       <c r="C299" t="n">
@@ -8824,7 +8812,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B300" s="2" t="n">
+      <c r="B300" s="1" t="n">
         <v>45446.80210648148</v>
       </c>
       <c r="C300" t="n">
@@ -8852,7 +8840,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B301" s="2" t="n">
+      <c r="B301" s="1" t="n">
         <v>45446.81251157408</v>
       </c>
       <c r="C301" t="n">
@@ -8880,7 +8868,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B302" s="2" t="n">
+      <c r="B302" s="1" t="n">
         <v>45446.82292824074</v>
       </c>
       <c r="C302" t="n">
@@ -8908,7 +8896,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B303" s="2" t="n">
+      <c r="B303" s="1" t="n">
         <v>45446.83334490741</v>
       </c>
       <c r="C303" t="n">
@@ -8936,7 +8924,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B304" s="2" t="n">
+      <c r="B304" s="1" t="n">
         <v>45446.84376157408</v>
       </c>
       <c r="C304" t="n">
@@ -8964,7 +8952,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B305" s="2" t="n">
+      <c r="B305" s="1" t="n">
         <v>45446.85417824074</v>
       </c>
       <c r="C305" t="n">
@@ -8992,7 +8980,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B306" s="2" t="n">
+      <c r="B306" s="1" t="n">
         <v>45446.86460648148</v>
       </c>
       <c r="C306" t="n">
@@ -9020,7 +9008,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B307" s="2" t="n">
+      <c r="B307" s="1" t="n">
         <v>45446.87502314815</v>
       </c>
       <c r="C307" t="n">
@@ -9048,7 +9036,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B308" s="2" t="n">
+      <c r="B308" s="1" t="n">
         <v>45446.88542824074</v>
       </c>
       <c r="C308" t="n">
@@ -9076,7 +9064,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B309" s="2" t="n">
+      <c r="B309" s="1" t="n">
         <v>45446.89584490741</v>
       </c>
       <c r="C309" t="n">
@@ -9104,7 +9092,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B310" s="2" t="n">
+      <c r="B310" s="1" t="n">
         <v>45446.90626157408</v>
       </c>
       <c r="C310" t="n">
@@ -9132,7 +9120,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B311" s="2" t="n">
+      <c r="B311" s="1" t="n">
         <v>45446.91667824074</v>
       </c>
       <c r="C311" t="n">
@@ -9160,7 +9148,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B312" s="2" t="n">
+      <c r="B312" s="1" t="n">
         <v>45446.92709490741</v>
       </c>
       <c r="C312" t="n">
@@ -9188,7 +9176,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B313" s="2" t="n">
+      <c r="B313" s="1" t="n">
         <v>45446.93751157408</v>
       </c>
       <c r="C313" t="n">
@@ -9216,7 +9204,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B314" s="2" t="n">
+      <c r="B314" s="1" t="n">
         <v>45446.94792824074</v>
       </c>
       <c r="C314" t="n">
@@ -9244,7 +9232,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B315" s="2" t="n">
+      <c r="B315" s="1" t="n">
         <v>45446.95834490741</v>
       </c>
       <c r="C315" t="n">
@@ -9272,7 +9260,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B316" s="2" t="n">
+      <c r="B316" s="1" t="n">
         <v>45446.96876157408</v>
       </c>
       <c r="C316" t="n">
@@ -9300,7 +9288,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B317" s="2" t="n">
+      <c r="B317" s="1" t="n">
         <v>45446.97917824074</v>
       </c>
       <c r="C317" t="n">
@@ -9328,7 +9316,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B318" s="2" t="n">
+      <c r="B318" s="1" t="n">
         <v>45446.98959490741</v>
       </c>
       <c r="C318" t="n">
@@ -9356,7 +9344,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B319" s="2" t="n">
+      <c r="B319" s="1" t="n">
         <v>45447.00001157408</v>
       </c>
       <c r="C319" t="n">
@@ -9384,7 +9372,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B320" s="2" t="n">
+      <c r="B320" s="1" t="n">
         <v>45447.01042824074</v>
       </c>
       <c r="C320" t="n">
@@ -9412,7 +9400,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B321" s="2" t="n">
+      <c r="B321" s="1" t="n">
         <v>45447.02084490741</v>
       </c>
       <c r="C321" t="n">
@@ -9440,7 +9428,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B322" s="2" t="n">
+      <c r="B322" s="1" t="n">
         <v>45447.03126157408</v>
       </c>
       <c r="C322" t="n">
@@ -9468,7 +9456,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B323" s="2" t="n">
+      <c r="B323" s="1" t="n">
         <v>45447.04167824074</v>
       </c>
       <c r="C323" t="n">
@@ -9496,7 +9484,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B324" s="2" t="n">
+      <c r="B324" s="1" t="n">
         <v>45447.05209490741</v>
       </c>
       <c r="C324" t="n">
@@ -9524,7 +9512,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B325" s="2" t="n">
+      <c r="B325" s="1" t="n">
         <v>45447.06251157408</v>
       </c>
       <c r="C325" t="n">
@@ -9552,7 +9540,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B326" s="2" t="n">
+      <c r="B326" s="1" t="n">
         <v>45447.07292824074</v>
       </c>
       <c r="C326" t="n">
@@ -9580,7 +9568,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B327" s="2" t="n">
+      <c r="B327" s="1" t="n">
         <v>45447.08334490741</v>
       </c>
       <c r="C327" t="n">
@@ -9608,7 +9596,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B328" s="2" t="n">
+      <c r="B328" s="1" t="n">
         <v>45447.09376157408</v>
       </c>
       <c r="C328" t="n">
@@ -9636,7 +9624,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B329" s="2" t="n">
+      <c r="B329" s="1" t="n">
         <v>45447.10417824074</v>
       </c>
       <c r="C329" t="n">
@@ -9664,7 +9652,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B330" s="2" t="n">
+      <c r="B330" s="1" t="n">
         <v>45447.11459490741</v>
       </c>
       <c r="C330" t="n">
@@ -9692,7 +9680,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B331" s="2" t="n">
+      <c r="B331" s="1" t="n">
         <v>45447.12501157408</v>
       </c>
       <c r="C331" t="n">
@@ -9720,7 +9708,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B332" s="2" t="n">
+      <c r="B332" s="1" t="n">
         <v>45447.13542824074</v>
       </c>
       <c r="C332" t="n">
@@ -9748,7 +9736,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B333" s="2" t="n">
+      <c r="B333" s="1" t="n">
         <v>45447.14584490741</v>
       </c>
       <c r="C333" t="n">
@@ -9776,7 +9764,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B334" s="2" t="n">
+      <c r="B334" s="1" t="n">
         <v>45447.15626157408</v>
       </c>
       <c r="C334" t="n">
@@ -9804,7 +9792,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B335" s="2" t="n">
+      <c r="B335" s="1" t="n">
         <v>45447.16667824074</v>
       </c>
       <c r="C335" t="n">
@@ -9832,7 +9820,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B336" s="2" t="n">
+      <c r="B336" s="1" t="n">
         <v>45447.17709490741</v>
       </c>
       <c r="C336" t="n">
@@ -9860,7 +9848,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B337" s="2" t="n">
+      <c r="B337" s="1" t="n">
         <v>45447.18751157408</v>
       </c>
       <c r="C337" t="n">
@@ -9888,7 +9876,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B338" s="2" t="n">
+      <c r="B338" s="1" t="n">
         <v>45447.19793981482</v>
       </c>
       <c r="C338" t="n">
@@ -9916,7 +9904,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B339" s="2" t="n">
+      <c r="B339" s="1" t="n">
         <v>45447.20835648148</v>
       </c>
       <c r="C339" t="n">
@@ -9944,7 +9932,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B340" s="2" t="n">
+      <c r="B340" s="1" t="n">
         <v>45447.21877314815</v>
       </c>
       <c r="C340" t="n">
@@ -9972,7 +9960,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B341" s="2" t="n">
+      <c r="B341" s="1" t="n">
         <v>45447.22918981482</v>
       </c>
       <c r="C341" t="n">
@@ -10000,7 +9988,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B342" s="2" t="n">
+      <c r="B342" s="1" t="n">
         <v>45447.23959490741</v>
       </c>
       <c r="C342" t="n">
@@ -10028,7 +10016,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B343" s="2" t="n">
+      <c r="B343" s="1" t="n">
         <v>45447.25001157408</v>
       </c>
       <c r="C343" t="n">
@@ -10056,7 +10044,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B344" s="2" t="n">
+      <c r="B344" s="1" t="n">
         <v>45447.26043981482</v>
       </c>
       <c r="C344" t="n">
@@ -10084,7 +10072,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B345" s="2" t="n">
+      <c r="B345" s="1" t="n">
         <v>45447.27084490741</v>
       </c>
       <c r="C345" t="n">
@@ -10112,7 +10100,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B346" s="2" t="n">
+      <c r="B346" s="1" t="n">
         <v>45447.28126157408</v>
       </c>
       <c r="C346" t="n">
@@ -10140,7 +10128,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B347" s="2" t="n">
+      <c r="B347" s="1" t="n">
         <v>45447.29167824074</v>
       </c>
       <c r="C347" t="n">
@@ -10168,7 +10156,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B348" s="2" t="n">
+      <c r="B348" s="1" t="n">
         <v>45447.30210648148</v>
       </c>
       <c r="C348" t="n">
@@ -10196,7 +10184,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B349" s="2" t="n">
+      <c r="B349" s="1" t="n">
         <v>45447.31252314815</v>
       </c>
       <c r="C349" t="n">
@@ -10224,7 +10212,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B350" s="2" t="n">
+      <c r="B350" s="1" t="n">
         <v>45447.32292824074</v>
       </c>
       <c r="C350" t="n">
@@ -10252,7 +10240,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B351" s="2" t="n">
+      <c r="B351" s="1" t="n">
         <v>45447.33334490741</v>
       </c>
       <c r="C351" t="n">
@@ -10280,7 +10268,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B352" s="2" t="n">
+      <c r="B352" s="1" t="n">
         <v>45447.34376157408</v>
       </c>
       <c r="C352" t="n">
@@ -10308,7 +10296,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B353" s="2" t="n">
+      <c r="B353" s="1" t="n">
         <v>45447.35417824074</v>
       </c>
       <c r="C353" t="n">
@@ -10336,7 +10324,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B354" s="2" t="n">
+      <c r="B354" s="1" t="n">
         <v>45447.36459490741</v>
       </c>
       <c r="C354" t="n">
@@ -10364,7 +10352,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B355" s="2" t="n">
+      <c r="B355" s="1" t="n">
         <v>45447.37502314815</v>
       </c>
       <c r="C355" t="n">
@@ -10392,7 +10380,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B356" s="2" t="n">
+      <c r="B356" s="1" t="n">
         <v>45447.38543981482</v>
       </c>
       <c r="C356" t="n">
@@ -10420,7 +10408,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B357" s="2" t="n">
+      <c r="B357" s="1" t="n">
         <v>45447.39584490741</v>
       </c>
       <c r="C357" t="n">
@@ -10448,7 +10436,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B358" s="2" t="n">
+      <c r="B358" s="1" t="n">
         <v>45447.40626157408</v>
       </c>
       <c r="C358" t="n">
@@ -10476,7 +10464,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B359" s="2" t="n">
+      <c r="B359" s="1" t="n">
         <v>45447.41667824074</v>
       </c>
       <c r="C359" t="n">
@@ -10504,7 +10492,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B360" s="2" t="n">
+      <c r="B360" s="1" t="n">
         <v>45447.42709490741</v>
       </c>
       <c r="C360" t="n">
@@ -10532,7 +10520,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B361" s="2" t="n">
+      <c r="B361" s="1" t="n">
         <v>45447.43751157408</v>
       </c>
       <c r="C361" t="n">
@@ -10560,7 +10548,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B362" s="2" t="n">
+      <c r="B362" s="1" t="n">
         <v>45447.44792824074</v>
       </c>
       <c r="C362" t="n">
@@ -10588,7 +10576,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B363" s="2" t="n">
+      <c r="B363" s="1" t="n">
         <v>45447.45834490741</v>
       </c>
       <c r="C363" t="n">
@@ -10616,7 +10604,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B364" s="2" t="n">
+      <c r="B364" s="1" t="n">
         <v>45447.46876157408</v>
       </c>
       <c r="C364" t="n">
@@ -10644,7 +10632,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B365" s="2" t="n">
+      <c r="B365" s="1" t="n">
         <v>45447.47917824074</v>
       </c>
       <c r="C365" t="n">
@@ -10672,7 +10660,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B366" s="2" t="n">
+      <c r="B366" s="1" t="n">
         <v>45447.48959490741</v>
       </c>
       <c r="C366" t="n">
@@ -10700,7 +10688,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B367" s="2" t="n">
+      <c r="B367" s="1" t="n">
         <v>45447.50001157408</v>
       </c>
       <c r="C367" t="n">
@@ -10728,7 +10716,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B368" s="2" t="n">
+      <c r="B368" s="1" t="n">
         <v>45447.51042824074</v>
       </c>
       <c r="C368" t="n">
@@ -10756,7 +10744,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B369" s="2" t="n">
+      <c r="B369" s="1" t="n">
         <v>45447.52084490741</v>
       </c>
       <c r="C369" t="n">
@@ -10784,7 +10772,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B370" s="2" t="n">
+      <c r="B370" s="1" t="n">
         <v>45447.53126157408</v>
       </c>
       <c r="C370" t="n">
@@ -10812,7 +10800,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B371" s="2" t="n">
+      <c r="B371" s="1" t="n">
         <v>45447.54167824074</v>
       </c>
       <c r="C371" t="n">
@@ -10840,7 +10828,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B372" s="2" t="n">
+      <c r="B372" s="1" t="n">
         <v>45447.55209490741</v>
       </c>
       <c r="C372" t="n">
@@ -10868,7 +10856,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B373" s="2" t="n">
+      <c r="B373" s="1" t="n">
         <v>45447.56251157408</v>
       </c>
       <c r="C373" t="n">
@@ -10896,7 +10884,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B374" s="2" t="n">
+      <c r="B374" s="1" t="n">
         <v>45447.57292824074</v>
       </c>
       <c r="C374" t="n">
@@ -10924,7 +10912,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B375" s="2" t="n">
+      <c r="B375" s="1" t="n">
         <v>45447.58334490741</v>
       </c>
       <c r="C375" t="n">
@@ -10952,7 +10940,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B376" s="2" t="n">
+      <c r="B376" s="1" t="n">
         <v>45447.59376157408</v>
       </c>
       <c r="C376" t="n">
@@ -10980,7 +10968,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B377" s="2" t="n">
+      <c r="B377" s="1" t="n">
         <v>45447.60417824074</v>
       </c>
       <c r="C377" t="n">
@@ -11008,7 +10996,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B378" s="2" t="n">
+      <c r="B378" s="1" t="n">
         <v>45447.61459490741</v>
       </c>
       <c r="C378" t="n">
@@ -11036,7 +11024,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B379" s="2" t="n">
+      <c r="B379" s="1" t="n">
         <v>45447.62501157408</v>
       </c>
       <c r="C379" t="n">
@@ -11064,7 +11052,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B380" s="2" t="n">
+      <c r="B380" s="1" t="n">
         <v>45447.63542824074</v>
       </c>
       <c r="C380" t="n">
@@ -11092,7 +11080,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B381" s="2" t="n">
+      <c r="B381" s="1" t="n">
         <v>45447.64584490741</v>
       </c>
       <c r="C381" t="n">
@@ -11120,7 +11108,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B382" s="2" t="n">
+      <c r="B382" s="1" t="n">
         <v>45447.65626157408</v>
       </c>
       <c r="C382" t="n">
@@ -11148,7 +11136,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B383" s="2" t="n">
+      <c r="B383" s="1" t="n">
         <v>45447.66667824074</v>
       </c>
       <c r="C383" t="n">
@@ -11176,7 +11164,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B384" s="2" t="n">
+      <c r="B384" s="1" t="n">
         <v>45447.67709490741</v>
       </c>
       <c r="C384" t="n">
@@ -11204,7 +11192,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B385" s="2" t="n">
+      <c r="B385" s="1" t="n">
         <v>45447.68751157408</v>
       </c>
       <c r="C385" t="n">
@@ -11232,7 +11220,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B386" s="2" t="n">
+      <c r="B386" s="1" t="n">
         <v>45447.69792824074</v>
       </c>
       <c r="C386" t="n">
@@ -11260,7 +11248,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B387" s="2" t="n">
+      <c r="B387" s="1" t="n">
         <v>45447.70834490741</v>
       </c>
       <c r="C387" t="n">
@@ -11288,7 +11276,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B388" s="2" t="n">
+      <c r="B388" s="1" t="n">
         <v>45447.71876157408</v>
       </c>
       <c r="C388" t="n">
@@ -11316,7 +11304,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B389" s="2" t="n">
+      <c r="B389" s="1" t="n">
         <v>45447.72917824074</v>
       </c>
       <c r="C389" t="n">
@@ -11344,7 +11332,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B390" s="2" t="n">
+      <c r="B390" s="1" t="n">
         <v>45447.73959490741</v>
       </c>
       <c r="C390" t="n">
@@ -11372,7 +11360,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B391" s="2" t="n">
+      <c r="B391" s="1" t="n">
         <v>45447.75001157408</v>
       </c>
       <c r="C391" t="n">
@@ -11400,7 +11388,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B392" s="2" t="n">
+      <c r="B392" s="1" t="n">
         <v>45447.76042824074</v>
       </c>
       <c r="C392" t="n">
@@ -11428,7 +11416,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B393" s="2" t="n">
+      <c r="B393" s="1" t="n">
         <v>45447.77084490741</v>
       </c>
       <c r="C393" t="n">
@@ -11456,7 +11444,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B394" s="2" t="n">
+      <c r="B394" s="1" t="n">
         <v>45447.78126157408</v>
       </c>
       <c r="C394" t="n">
@@ -11484,7 +11472,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B395" s="2" t="n">
+      <c r="B395" s="1" t="n">
         <v>45447.79167824074</v>
       </c>
       <c r="C395" t="n">
@@ -11512,7 +11500,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B396" s="2" t="n">
+      <c r="B396" s="1" t="n">
         <v>45447.80209490741</v>
       </c>
       <c r="C396" t="n">
@@ -11540,7 +11528,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B397" s="2" t="n">
+      <c r="B397" s="1" t="n">
         <v>45447.81251157408</v>
       </c>
       <c r="C397" t="n">
@@ -11568,7 +11556,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B398" s="2" t="n">
+      <c r="B398" s="1" t="n">
         <v>45447.82292824074</v>
       </c>
       <c r="C398" t="n">
@@ -11596,7 +11584,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B399" s="2" t="n">
+      <c r="B399" s="1" t="n">
         <v>45447.83335648148</v>
       </c>
       <c r="C399" t="n">
@@ -11624,7 +11612,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B400" s="2" t="n">
+      <c r="B400" s="1" t="n">
         <v>45447.84377314815</v>
       </c>
       <c r="C400" t="n">
@@ -11652,7 +11640,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B401" s="2" t="n">
+      <c r="B401" s="1" t="n">
         <v>45447.85418981482</v>
       </c>
       <c r="C401" t="n">
@@ -11680,7 +11668,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B402" s="2" t="n">
+      <c r="B402" s="1" t="n">
         <v>45447.86459490741</v>
       </c>
       <c r="C402" t="n">
@@ -11708,7 +11696,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B403" s="2" t="n">
+      <c r="B403" s="1" t="n">
         <v>45447.87501157408</v>
       </c>
       <c r="C403" t="n">
@@ -11736,7 +11724,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B404" s="2" t="n">
+      <c r="B404" s="1" t="n">
         <v>45447.88542824074</v>
       </c>
       <c r="C404" t="n">
@@ -11764,7 +11752,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B405" s="2" t="n">
+      <c r="B405" s="1" t="n">
         <v>45447.89585648148</v>
       </c>
       <c r="C405" t="n">
@@ -11792,7 +11780,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B406" s="2" t="n">
+      <c r="B406" s="1" t="n">
         <v>45447.90626157408</v>
       </c>
       <c r="C406" t="n">
@@ -11820,7 +11808,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B407" s="2" t="n">
+      <c r="B407" s="1" t="n">
         <v>45447.91667824074</v>
       </c>
       <c r="C407" t="n">
@@ -11848,7 +11836,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B408" s="2" t="n">
+      <c r="B408" s="1" t="n">
         <v>45447.92710648148</v>
       </c>
       <c r="C408" t="n">
@@ -11876,7 +11864,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B409" s="2" t="n">
+      <c r="B409" s="1" t="n">
         <v>45447.93752314815</v>
       </c>
       <c r="C409" t="n">
@@ -11904,7 +11892,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B410" s="2" t="n">
+      <c r="B410" s="1" t="n">
         <v>45447.94793981482</v>
       </c>
       <c r="C410" t="n">
@@ -11932,7 +11920,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B411" s="2" t="n">
+      <c r="B411" s="1" t="n">
         <v>45447.95834490741</v>
       </c>
       <c r="C411" t="n">
@@ -11960,7 +11948,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B412" s="2" t="n">
+      <c r="B412" s="1" t="n">
         <v>45447.96876157408</v>
       </c>
       <c r="C412" t="n">
@@ -11988,7 +11976,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B413" s="2" t="n">
+      <c r="B413" s="1" t="n">
         <v>45447.97917824074</v>
       </c>
       <c r="C413" t="n">
@@ -12016,7 +12004,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B414" s="2" t="n">
+      <c r="B414" s="1" t="n">
         <v>45447.98959490741</v>
       </c>
       <c r="C414" t="n">
@@ -12044,7 +12032,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B415" s="2" t="n">
+      <c r="B415" s="1" t="n">
         <v>45448.00001157408</v>
       </c>
       <c r="C415" t="n">
@@ -12072,7 +12060,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B416" s="2" t="n">
+      <c r="B416" s="1" t="n">
         <v>45448.01042824074</v>
       </c>
       <c r="C416" t="n">
@@ -12100,7 +12088,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B417" s="2" t="n">
+      <c r="B417" s="1" t="n">
         <v>45448.02084490741</v>
       </c>
       <c r="C417" t="n">
@@ -12128,7 +12116,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B418" s="2" t="n">
+      <c r="B418" s="1" t="n">
         <v>45448.03126157408</v>
       </c>
       <c r="C418" t="n">
@@ -12156,7 +12144,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B419" s="2" t="n">
+      <c r="B419" s="1" t="n">
         <v>45448.04167824074</v>
       </c>
       <c r="C419" t="n">
@@ -12184,7 +12172,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B420" s="2" t="n">
+      <c r="B420" s="1" t="n">
         <v>45448.05209490741</v>
       </c>
       <c r="C420" t="n">
@@ -12212,7 +12200,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B421" s="2" t="n">
+      <c r="B421" s="1" t="n">
         <v>45448.06251157408</v>
       </c>
       <c r="C421" t="n">
@@ -12240,7 +12228,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B422" s="2" t="n">
+      <c r="B422" s="1" t="n">
         <v>45448.07292824074</v>
       </c>
       <c r="C422" t="n">
@@ -12268,7 +12256,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B423" s="2" t="n">
+      <c r="B423" s="1" t="n">
         <v>45448.08334490741</v>
       </c>
       <c r="C423" t="n">
@@ -12296,7 +12284,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B424" s="2" t="n">
+      <c r="B424" s="1" t="n">
         <v>45448.09376157408</v>
       </c>
       <c r="C424" t="n">
@@ -12324,7 +12312,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B425" s="2" t="n">
+      <c r="B425" s="1" t="n">
         <v>45448.10417824074</v>
       </c>
       <c r="C425" t="n">
@@ -12352,7 +12340,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B426" s="2" t="n">
+      <c r="B426" s="1" t="n">
         <v>45448.11459490741</v>
       </c>
       <c r="C426" t="n">
@@ -12380,7 +12368,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B427" s="2" t="n">
+      <c r="B427" s="1" t="n">
         <v>45448.12501157408</v>
       </c>
       <c r="C427" t="n">
@@ -12408,7 +12396,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B428" s="2" t="n">
+      <c r="B428" s="1" t="n">
         <v>45448.13542824074</v>
       </c>
       <c r="C428" t="n">
@@ -12436,7 +12424,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B429" s="2" t="n">
+      <c r="B429" s="1" t="n">
         <v>45448.14584490741</v>
       </c>
       <c r="C429" t="n">
@@ -12464,7 +12452,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B430" s="2" t="n">
+      <c r="B430" s="1" t="n">
         <v>45448.15626157408</v>
       </c>
       <c r="C430" t="n">
@@ -12492,7 +12480,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B431" s="2" t="n">
+      <c r="B431" s="1" t="n">
         <v>45448.16667824074</v>
       </c>
       <c r="C431" t="n">
@@ -12520,7 +12508,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B432" s="2" t="n">
+      <c r="B432" s="1" t="n">
         <v>45448.17709490741</v>
       </c>
       <c r="C432" t="n">
@@ -12548,7 +12536,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B433" s="2" t="n">
+      <c r="B433" s="1" t="n">
         <v>45448.18751157408</v>
       </c>
       <c r="C433" t="n">
@@ -12576,7 +12564,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B434" s="2" t="n">
+      <c r="B434" s="1" t="n">
         <v>45448.19792824074</v>
       </c>
       <c r="C434" t="n">
@@ -12604,7 +12592,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B435" s="2" t="n">
+      <c r="B435" s="1" t="n">
         <v>45448.20835648148</v>
       </c>
       <c r="C435" t="n">
@@ -12632,7 +12620,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B436" s="2" t="n">
+      <c r="B436" s="1" t="n">
         <v>45448.21876157408</v>
       </c>
       <c r="C436" t="n">
@@ -12660,7 +12648,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B437" s="2" t="n">
+      <c r="B437" s="1" t="n">
         <v>45448.22917824074</v>
       </c>
       <c r="C437" t="n">
@@ -12688,7 +12676,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B438" s="2" t="n">
+      <c r="B438" s="1" t="n">
         <v>45448.23959490741</v>
       </c>
       <c r="C438" t="n">
@@ -12716,7 +12704,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B439" s="2" t="n">
+      <c r="B439" s="1" t="n">
         <v>45448.25001157408</v>
       </c>
       <c r="C439" t="n">
@@ -12744,7 +12732,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B440" s="2" t="n">
+      <c r="B440" s="1" t="n">
         <v>45448.26043981482</v>
       </c>
       <c r="C440" t="n">
@@ -12772,7 +12760,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B441" s="2" t="n">
+      <c r="B441" s="1" t="n">
         <v>45448.27085648148</v>
       </c>
       <c r="C441" t="n">
@@ -12800,7 +12788,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B442" s="2" t="n">
+      <c r="B442" s="1" t="n">
         <v>45448.28127314815</v>
       </c>
       <c r="C442" t="n">
@@ -12828,7 +12816,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B443" s="2" t="n">
+      <c r="B443" s="1" t="n">
         <v>45448.29167824074</v>
       </c>
       <c r="C443" t="n">
@@ -12856,7 +12844,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B444" s="2" t="n">
+      <c r="B444" s="1" t="n">
         <v>45448.30209490741</v>
       </c>
       <c r="C444" t="n">
@@ -12884,7 +12872,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B445" s="2" t="n">
+      <c r="B445" s="1" t="n">
         <v>45448.31251157408</v>
       </c>
       <c r="C445" t="n">
@@ -12912,7 +12900,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B446" s="2" t="n">
+      <c r="B446" s="1" t="n">
         <v>45448.32292824074</v>
       </c>
       <c r="C446" t="n">
@@ -12940,7 +12928,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B447" s="2" t="n">
+      <c r="B447" s="1" t="n">
         <v>45448.33335648148</v>
       </c>
       <c r="C447" t="n">
@@ -12968,7 +12956,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B448" s="2" t="n">
+      <c r="B448" s="1" t="n">
         <v>45448.34377314815</v>
       </c>
       <c r="C448" t="n">
@@ -12996,7 +12984,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B449" s="2" t="n">
+      <c r="B449" s="1" t="n">
         <v>45448.35418981482</v>
       </c>
       <c r="C449" t="n">
@@ -13024,7 +13012,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B450" s="2" t="n">
+      <c r="B450" s="1" t="n">
         <v>45448.36460648148</v>
       </c>
       <c r="C450" t="n">
@@ -13052,7 +13040,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B451" s="2" t="n">
+      <c r="B451" s="1" t="n">
         <v>45448.37501157408</v>
       </c>
       <c r="C451" t="n">
@@ -13080,7 +13068,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B452" s="2" t="n">
+      <c r="B452" s="1" t="n">
         <v>45448.38542824074</v>
       </c>
       <c r="C452" t="n">
@@ -13108,7 +13096,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B453" s="2" t="n">
+      <c r="B453" s="1" t="n">
         <v>45448.39584490741</v>
       </c>
       <c r="C453" t="n">
@@ -13136,7 +13124,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B454" s="2" t="n">
+      <c r="B454" s="1" t="n">
         <v>45448.40626157408</v>
       </c>
       <c r="C454" t="n">
@@ -13164,7 +13152,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B455" s="2" t="n">
+      <c r="B455" s="1" t="n">
         <v>45448.41667824074</v>
       </c>
       <c r="C455" t="n">
@@ -13192,7 +13180,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B456" s="2" t="n">
+      <c r="B456" s="1" t="n">
         <v>45448.42709490741</v>
       </c>
       <c r="C456" t="n">
@@ -13220,7 +13208,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B457" s="2" t="n">
+      <c r="B457" s="1" t="n">
         <v>45448.43752314815</v>
       </c>
       <c r="C457" t="n">
@@ -13248,7 +13236,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B458" s="2" t="n">
+      <c r="B458" s="1" t="n">
         <v>45448.44793981482</v>
       </c>
       <c r="C458" t="n">
@@ -13276,7 +13264,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B459" s="2" t="n">
+      <c r="B459" s="1" t="n">
         <v>45448.45835648148</v>
       </c>
       <c r="C459" t="n">
@@ -13304,7 +13292,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B460" s="2" t="n">
+      <c r="B460" s="1" t="n">
         <v>45448.46876157408</v>
       </c>
       <c r="C460" t="n">
@@ -13332,7 +13320,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B461" s="2" t="n">
+      <c r="B461" s="1" t="n">
         <v>45448.47917824074</v>
       </c>
       <c r="C461" t="n">
@@ -13360,7 +13348,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B462" s="2" t="n">
+      <c r="B462" s="1" t="n">
         <v>45448.48959490741</v>
       </c>
       <c r="C462" t="n">
@@ -13388,7 +13376,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B463" s="2" t="n">
+      <c r="B463" s="1" t="n">
         <v>45448.50002314815</v>
       </c>
       <c r="C463" t="n">
@@ -13416,7 +13404,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B464" s="2" t="n">
+      <c r="B464" s="1" t="n">
         <v>45448.51043981482</v>
       </c>
       <c r="C464" t="n">
@@ -13444,7 +13432,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B465" s="2" t="n">
+      <c r="B465" s="1" t="n">
         <v>45448.52085648148</v>
       </c>
       <c r="C465" t="n">
@@ -13472,7 +13460,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B466" s="2" t="n">
+      <c r="B466" s="1" t="n">
         <v>45448.53127314815</v>
       </c>
       <c r="C466" t="n">
@@ -13500,7 +13488,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B467" s="2" t="n">
+      <c r="B467" s="1" t="n">
         <v>45448.54167824074</v>
       </c>
       <c r="C467" t="n">
@@ -13528,7 +13516,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B468" s="2" t="n">
+      <c r="B468" s="1" t="n">
         <v>45448.55209490741</v>
       </c>
       <c r="C468" t="n">
@@ -13556,7 +13544,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B469" s="2" t="n">
+      <c r="B469" s="1" t="n">
         <v>45448.56251157408</v>
       </c>
       <c r="C469" t="n">
@@ -13584,7 +13572,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B470" s="2" t="n">
+      <c r="B470" s="1" t="n">
         <v>45448.57292824074</v>
       </c>
       <c r="C470" t="n">
@@ -13612,7 +13600,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B471" s="2" t="n">
+      <c r="B471" s="1" t="n">
         <v>45448.58335648148</v>
       </c>
       <c r="C471" t="n">
@@ -13640,7 +13628,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B472" s="2" t="n">
+      <c r="B472" s="1" t="n">
         <v>45448.59377314815</v>
       </c>
       <c r="C472" t="n">
@@ -13668,7 +13656,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B473" s="2" t="n">
+      <c r="B473" s="1" t="n">
         <v>45448.60418981482</v>
       </c>
       <c r="C473" t="n">
@@ -13696,7 +13684,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B474" s="2" t="n">
+      <c r="B474" s="1" t="n">
         <v>45448.61459490741</v>
       </c>
       <c r="C474" t="n">
@@ -13724,7 +13712,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B475" s="2" t="n">
+      <c r="B475" s="1" t="n">
         <v>45448.62501157408</v>
       </c>
       <c r="C475" t="n">
@@ -13752,7 +13740,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B476" s="2" t="n">
+      <c r="B476" s="1" t="n">
         <v>45448.63542824074</v>
       </c>
       <c r="C476" t="n">
@@ -13780,7 +13768,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B477" s="2" t="n">
+      <c r="B477" s="1" t="n">
         <v>45448.64585648148</v>
       </c>
       <c r="C477" t="n">
@@ -13808,7 +13796,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B478" s="2" t="n">
+      <c r="B478" s="1" t="n">
         <v>45448.65627314815</v>
       </c>
       <c r="C478" t="n">
@@ -13836,7 +13824,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B479" s="2" t="n">
+      <c r="B479" s="1" t="n">
         <v>45448.66667824074</v>
       </c>
       <c r="C479" t="n">
@@ -13864,7 +13852,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B480" s="2" t="n">
+      <c r="B480" s="1" t="n">
         <v>45448.67709490741</v>
       </c>
       <c r="C480" t="n">
@@ -13892,7 +13880,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B481" s="2" t="n">
+      <c r="B481" s="1" t="n">
         <v>45448.68751157408</v>
       </c>
       <c r="C481" t="n">
@@ -13920,7 +13908,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B482" s="2" t="n">
+      <c r="B482" s="1" t="n">
         <v>45448.69793981482</v>
       </c>
       <c r="C482" t="n">
@@ -13948,7 +13936,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B483" s="2" t="n">
+      <c r="B483" s="1" t="n">
         <v>45448.70835648148</v>
       </c>
       <c r="C483" t="n">
@@ -13976,7 +13964,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B484" s="2" t="n">
+      <c r="B484" s="1" t="n">
         <v>45448.71876157408</v>
       </c>
       <c r="C484" t="n">
@@ -14004,7 +13992,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B485" s="2" t="n">
+      <c r="B485" s="1" t="n">
         <v>45448.72917824074</v>
       </c>
       <c r="C485" t="n">
@@ -14032,7 +14020,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B486" s="2" t="n">
+      <c r="B486" s="1" t="n">
         <v>45448.73959490741</v>
       </c>
       <c r="C486" t="n">
@@ -14060,7 +14048,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B487" s="2" t="n">
+      <c r="B487" s="1" t="n">
         <v>45448.75001157408</v>
       </c>
       <c r="C487" t="n">
@@ -14088,7 +14076,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B488" s="2" t="n">
+      <c r="B488" s="1" t="n">
         <v>45448.76043981482</v>
       </c>
       <c r="C488" t="n">
@@ -14116,7 +14104,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B489" s="2" t="n">
+      <c r="B489" s="1" t="n">
         <v>45448.77085648148</v>
       </c>
       <c r="C489" t="n">
@@ -14144,7 +14132,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B490" s="2" t="n">
+      <c r="B490" s="1" t="n">
         <v>45448.78127314815</v>
       </c>
       <c r="C490" t="n">
@@ -14172,7 +14160,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B491" s="2" t="n">
+      <c r="B491" s="1" t="n">
         <v>45448.79168981482</v>
       </c>
       <c r="C491" t="n">
@@ -14200,7 +14188,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B492" s="2" t="n">
+      <c r="B492" s="1" t="n">
         <v>45448.80209490741</v>
       </c>
       <c r="C492" t="n">
@@ -14228,7 +14216,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B493" s="2" t="n">
+      <c r="B493" s="1" t="n">
         <v>45448.81252314815</v>
       </c>
       <c r="C493" t="n">
@@ -14256,7 +14244,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B494" s="2" t="n">
+      <c r="B494" s="1" t="n">
         <v>45448.82292824074</v>
       </c>
       <c r="C494" t="n">
@@ -14284,7 +14272,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B495" s="2" t="n">
+      <c r="B495" s="1" t="n">
         <v>45448.83334490741</v>
       </c>
       <c r="C495" t="n">
@@ -14312,7 +14300,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B496" s="2" t="n">
+      <c r="B496" s="1" t="n">
         <v>45448.84376157408</v>
       </c>
       <c r="C496" t="n">
@@ -14340,7 +14328,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B497" s="2" t="n">
+      <c r="B497" s="1" t="n">
         <v>45448.85418981482</v>
       </c>
       <c r="C497" t="n">
@@ -14368,7 +14356,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B498" s="2" t="n">
+      <c r="B498" s="1" t="n">
         <v>45448.86460648148</v>
       </c>
       <c r="C498" t="n">
@@ -14396,7 +14384,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B499" s="2" t="n">
+      <c r="B499" s="1" t="n">
         <v>45448.87501157408</v>
       </c>
       <c r="C499" t="n">
@@ -14424,7 +14412,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B500" s="2" t="n">
+      <c r="B500" s="1" t="n">
         <v>45448.88542824074</v>
       </c>
       <c r="C500" t="n">
@@ -14452,7 +14440,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B501" s="2" t="n">
+      <c r="B501" s="1" t="n">
         <v>45448.89585648148</v>
       </c>
       <c r="C501" t="n">
@@ -14480,7 +14468,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B502" s="2" t="n">
+      <c r="B502" s="1" t="n">
         <v>45448.90626157408</v>
       </c>
       <c r="C502" t="n">
@@ -14508,7 +14496,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B503" s="2" t="n">
+      <c r="B503" s="1" t="n">
         <v>45448.91667824074</v>
       </c>
       <c r="C503" t="n">
@@ -14536,7 +14524,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B504" s="2" t="n">
+      <c r="B504" s="1" t="n">
         <v>45448.92710648148</v>
       </c>
       <c r="C504" t="n">
@@ -14564,7 +14552,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B505" s="2" t="n">
+      <c r="B505" s="1" t="n">
         <v>45448.93752314815</v>
       </c>
       <c r="C505" t="n">
@@ -14592,7 +14580,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B506" s="2" t="n">
+      <c r="B506" s="1" t="n">
         <v>45448.94793981482</v>
       </c>
       <c r="C506" t="n">
@@ -14620,7 +14608,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B507" s="2" t="n">
+      <c r="B507" s="1" t="n">
         <v>45448.95834490741</v>
       </c>
       <c r="C507" t="n">
@@ -14648,7 +14636,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B508" s="2" t="n">
+      <c r="B508" s="1" t="n">
         <v>45448.96876157408</v>
       </c>
       <c r="C508" t="n">
@@ -14676,7 +14664,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B509" s="2" t="n">
+      <c r="B509" s="1" t="n">
         <v>45448.97917824074</v>
       </c>
       <c r="C509" t="n">
@@ -14704,7 +14692,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B510" s="2" t="n">
+      <c r="B510" s="1" t="n">
         <v>45448.98959490741</v>
       </c>
       <c r="C510" t="n">
@@ -14732,7 +14720,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B511" s="2" t="n">
+      <c r="B511" s="1" t="n">
         <v>45449.00001157408</v>
       </c>
       <c r="C511" t="n">
@@ -14760,7 +14748,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B512" s="2" t="n">
+      <c r="B512" s="1" t="n">
         <v>45449.01043981482</v>
       </c>
       <c r="C512" t="n">
@@ -14788,7 +14776,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B513" s="2" t="n">
+      <c r="B513" s="1" t="n">
         <v>45449.02085648148</v>
       </c>
       <c r="C513" t="n">
@@ -14816,7 +14804,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B514" s="2" t="n">
+      <c r="B514" s="1" t="n">
         <v>45449.03126157408</v>
       </c>
       <c r="C514" t="n">
@@ -14844,7 +14832,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B515" s="2" t="n">
+      <c r="B515" s="1" t="n">
         <v>45449.04167824074</v>
       </c>
       <c r="C515" t="n">
@@ -14872,7 +14860,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B516" s="2" t="n">
+      <c r="B516" s="1" t="n">
         <v>45449.05209490741</v>
       </c>
       <c r="C516" t="n">
@@ -14900,7 +14888,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B517" s="2" t="n">
+      <c r="B517" s="1" t="n">
         <v>45449.06251157408</v>
       </c>
       <c r="C517" t="n">
@@ -14928,7 +14916,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B518" s="2" t="n">
+      <c r="B518" s="1" t="n">
         <v>45449.07292824074</v>
       </c>
       <c r="C518" t="n">
@@ -14956,7 +14944,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B519" s="2" t="n">
+      <c r="B519" s="1" t="n">
         <v>45449.08334490741</v>
       </c>
       <c r="C519" t="n">
@@ -14984,7 +14972,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B520" s="2" t="n">
+      <c r="B520" s="1" t="n">
         <v>45449.09376157408</v>
       </c>
       <c r="C520" t="n">
@@ -15012,7 +15000,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B521" s="2" t="n">
+      <c r="B521" s="1" t="n">
         <v>45449.10417824074</v>
       </c>
       <c r="C521" t="n">
@@ -15040,7 +15028,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B522" s="2" t="n">
+      <c r="B522" s="1" t="n">
         <v>45449.11459490741</v>
       </c>
       <c r="C522" t="n">
@@ -15068,7 +15056,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B523" s="2" t="n">
+      <c r="B523" s="1" t="n">
         <v>45449.12501157408</v>
       </c>
       <c r="C523" t="n">
@@ -15096,7 +15084,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B524" s="2" t="n">
+      <c r="B524" s="1" t="n">
         <v>45449.13542824074</v>
       </c>
       <c r="C524" t="n">
@@ -15124,7 +15112,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B525" s="2" t="n">
+      <c r="B525" s="1" t="n">
         <v>45449.14584490741</v>
       </c>
       <c r="C525" t="n">
@@ -15152,7 +15140,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B526" s="2" t="n">
+      <c r="B526" s="1" t="n">
         <v>45449.15626157408</v>
       </c>
       <c r="C526" t="n">
@@ -15180,7 +15168,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B527" s="2" t="n">
+      <c r="B527" s="1" t="n">
         <v>45449.16667824074</v>
       </c>
       <c r="C527" t="n">
@@ -15208,7 +15196,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B528" s="2" t="n">
+      <c r="B528" s="1" t="n">
         <v>45449.17709490741</v>
       </c>
       <c r="C528" t="n">
@@ -15236,7 +15224,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B529" s="2" t="n">
+      <c r="B529" s="1" t="n">
         <v>45449.18751157408</v>
       </c>
       <c r="C529" t="n">
@@ -15264,7 +15252,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B530" s="2" t="n">
+      <c r="B530" s="1" t="n">
         <v>45449.19792824074</v>
       </c>
       <c r="C530" t="n">
@@ -15292,7 +15280,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B531" s="2" t="n">
+      <c r="B531" s="1" t="n">
         <v>45449.20834490741</v>
       </c>
       <c r="C531" t="n">
@@ -15320,7 +15308,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B532" s="2" t="n">
+      <c r="B532" s="1" t="n">
         <v>45449.21876157408</v>
       </c>
       <c r="C532" t="n">
@@ -15348,7 +15336,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B533" s="2" t="n">
+      <c r="B533" s="1" t="n">
         <v>45449.22917824074</v>
       </c>
       <c r="C533" t="n">
@@ -15376,7 +15364,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B534" s="2" t="n">
+      <c r="B534" s="1" t="n">
         <v>45449.23959490741</v>
       </c>
       <c r="C534" t="n">
@@ -15404,7 +15392,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B535" s="2" t="n">
+      <c r="B535" s="1" t="n">
         <v>45449.25001157408</v>
       </c>
       <c r="C535" t="n">
@@ -15432,7 +15420,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B536" s="2" t="n">
+      <c r="B536" s="1" t="n">
         <v>45449.26042824074</v>
       </c>
       <c r="C536" t="n">
@@ -15460,7 +15448,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B537" s="2" t="n">
+      <c r="B537" s="1" t="n">
         <v>45449.27084490741</v>
       </c>
       <c r="C537" t="n">
@@ -15488,7 +15476,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B538" s="2" t="n">
+      <c r="B538" s="1" t="n">
         <v>45449.28126157408</v>
       </c>
       <c r="C538" t="n">
@@ -15516,7 +15504,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B539" s="2" t="n">
+      <c r="B539" s="1" t="n">
         <v>45449.29167824074</v>
       </c>
       <c r="C539" t="n">
@@ -15544,7 +15532,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B540" s="2" t="n">
+      <c r="B540" s="1" t="n">
         <v>45449.30209490741</v>
       </c>
       <c r="C540" t="n">
@@ -15572,7 +15560,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B541" s="2" t="n">
+      <c r="B541" s="1" t="n">
         <v>45449.31251157408</v>
       </c>
       <c r="C541" t="n">
@@ -15600,7 +15588,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B542" s="2" t="n">
+      <c r="B542" s="1" t="n">
         <v>45449.32292824074</v>
       </c>
       <c r="C542" t="n">
@@ -15628,7 +15616,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B543" s="2" t="n">
+      <c r="B543" s="1" t="n">
         <v>45449.33334490741</v>
       </c>
       <c r="C543" t="n">
@@ -15656,7 +15644,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B544" s="2" t="n">
+      <c r="B544" s="1" t="n">
         <v>45449.34376157408</v>
       </c>
       <c r="C544" t="n">
@@ -15684,7 +15672,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B545" s="2" t="n">
+      <c r="B545" s="1" t="n">
         <v>45449.35417824074</v>
       </c>
       <c r="C545" t="n">
@@ -15712,7 +15700,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B546" s="2" t="n">
+      <c r="B546" s="1" t="n">
         <v>45449.36459490741</v>
       </c>
       <c r="C546" t="n">
@@ -15740,7 +15728,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B547" s="2" t="n">
+      <c r="B547" s="1" t="n">
         <v>45449.37501157408</v>
       </c>
       <c r="C547" t="n">
@@ -15768,7 +15756,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B548" s="2" t="n">
+      <c r="B548" s="1" t="n">
         <v>45449.38543981482</v>
       </c>
       <c r="C548" t="n">
@@ -15796,7 +15784,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B549" s="2" t="n">
+      <c r="B549" s="1" t="n">
         <v>45449.39585648148</v>
       </c>
       <c r="C549" t="n">
@@ -15824,7 +15812,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B550" s="2" t="n">
+      <c r="B550" s="1" t="n">
         <v>45449.40626157408</v>
       </c>
       <c r="C550" t="n">
@@ -15852,7 +15840,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B551" s="2" t="n">
+      <c r="B551" s="1" t="n">
         <v>45449.41667824074</v>
       </c>
       <c r="C551" t="n">
@@ -15880,7 +15868,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B552" s="2" t="n">
+      <c r="B552" s="1" t="n">
         <v>45449.42709490741</v>
       </c>
       <c r="C552" t="n">
@@ -15908,7 +15896,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B553" s="2" t="n">
+      <c r="B553" s="1" t="n">
         <v>45449.43751157408</v>
       </c>
       <c r="C553" t="n">
@@ -15936,7 +15924,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B554" s="2" t="n">
+      <c r="B554" s="1" t="n">
         <v>45449.44793981482</v>
       </c>
       <c r="C554" t="n">
@@ -15964,7 +15952,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B555" s="2" t="n">
+      <c r="B555" s="1" t="n">
         <v>45449.45834490741</v>
       </c>
       <c r="C555" t="n">
@@ -15992,7 +15980,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B556" s="2" t="n">
+      <c r="B556" s="1" t="n">
         <v>45449.46877314815</v>
       </c>
       <c r="C556" t="n">
@@ -16020,7 +16008,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B557" s="2" t="n">
+      <c r="B557" s="1" t="n">
         <v>45449.47918981482</v>
       </c>
       <c r="C557" t="n">
@@ -16048,7 +16036,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B558" s="2" t="n">
+      <c r="B558" s="1" t="n">
         <v>45449.48960648148</v>
       </c>
       <c r="C558" t="n">
@@ -16076,7 +16064,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B559" s="2" t="n">
+      <c r="B559" s="1" t="n">
         <v>45449.50001157408</v>
       </c>
       <c r="C559" t="n">
@@ -16104,7 +16092,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B560" s="2" t="n">
+      <c r="B560" s="1" t="n">
         <v>45449.51042824074</v>
       </c>
       <c r="C560" t="n">
@@ -16132,7 +16120,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B561" s="2" t="n">
+      <c r="B561" s="1" t="n">
         <v>45449.52084490741</v>
       </c>
       <c r="C561" t="n">
@@ -16160,7 +16148,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B562" s="2" t="n">
+      <c r="B562" s="1" t="n">
         <v>45449.53127314815</v>
       </c>
       <c r="C562" t="n">
@@ -16188,7 +16176,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B563" s="2" t="n">
+      <c r="B563" s="1" t="n">
         <v>45449.54168981482</v>
       </c>
       <c r="C563" t="n">
@@ -16216,7 +16204,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B564" s="2" t="n">
+      <c r="B564" s="1" t="n">
         <v>45449.55210648148</v>
       </c>
       <c r="C564" t="n">
@@ -16244,7 +16232,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B565" s="2" t="n">
+      <c r="B565" s="1" t="n">
         <v>45449.56251157408</v>
       </c>
       <c r="C565" t="n">
@@ -16272,7 +16260,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B566" s="2" t="n">
+      <c r="B566" s="1" t="n">
         <v>45449.57293981482</v>
       </c>
       <c r="C566" t="n">
@@ -16300,7 +16288,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B567" s="2" t="n">
+      <c r="B567" s="1" t="n">
         <v>45449.58334490741</v>
       </c>
       <c r="C567" t="n">
@@ -16328,7 +16316,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B568" s="2" t="n">
+      <c r="B568" s="1" t="n">
         <v>45449.59376157408</v>
       </c>
       <c r="C568" t="n">
@@ -16356,7 +16344,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B569" s="2" t="n">
+      <c r="B569" s="1" t="n">
         <v>45449.60417824074</v>
       </c>
       <c r="C569" t="n">
@@ -16384,7 +16372,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B570" s="2" t="n">
+      <c r="B570" s="1" t="n">
         <v>45449.61460648148</v>
       </c>
       <c r="C570" t="n">
@@ -16412,7 +16400,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B571" s="2" t="n">
+      <c r="B571" s="1" t="n">
         <v>45449.62502314815</v>
       </c>
       <c r="C571" t="n">
@@ -16440,7 +16428,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B572" s="2" t="n">
+      <c r="B572" s="1" t="n">
         <v>45449.63543981482</v>
       </c>
       <c r="C572" t="n">
@@ -16468,7 +16456,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B573" s="2" t="n">
+      <c r="B573" s="1" t="n">
         <v>45449.64585648148</v>
       </c>
       <c r="C573" t="n">
@@ -16496,7 +16484,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B574" s="2" t="n">
+      <c r="B574" s="1" t="n">
         <v>45449.65626157408</v>
       </c>
       <c r="C574" t="n">
@@ -16524,7 +16512,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B575" s="2" t="n">
+      <c r="B575" s="1" t="n">
         <v>45449.66667824074</v>
       </c>
       <c r="C575" t="n">
@@ -16552,7 +16540,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B576" s="2" t="n">
+      <c r="B576" s="1" t="n">
         <v>45449.67709490741</v>
       </c>
       <c r="C576" t="n">
@@ -16580,7 +16568,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B577" s="2" t="n">
+      <c r="B577" s="1" t="n">
         <v>45449.68751157408</v>
       </c>
       <c r="C577" t="n">
@@ -16608,7 +16596,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B578" s="2" t="n">
+      <c r="B578" s="1" t="n">
         <v>45449.69792824074</v>
       </c>
       <c r="C578" t="n">
@@ -16636,7 +16624,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B579" s="2" t="n">
+      <c r="B579" s="1" t="n">
         <v>45449.70835648148</v>
       </c>
       <c r="C579" t="n">
@@ -16664,7 +16652,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B580" s="2" t="n">
+      <c r="B580" s="1" t="n">
         <v>45449.71877314815</v>
       </c>
       <c r="C580" t="n">
@@ -16692,7 +16680,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B581" s="2" t="n">
+      <c r="B581" s="1" t="n">
         <v>45449.72917824074</v>
       </c>
       <c r="C581" t="n">
@@ -16720,7 +16708,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B582" s="2" t="n">
+      <c r="B582" s="1" t="n">
         <v>45449.73959490741</v>
       </c>
       <c r="C582" t="n">
@@ -16748,7 +16736,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B583" s="2" t="n">
+      <c r="B583" s="1" t="n">
         <v>45449.75001157408</v>
       </c>
       <c r="C583" t="n">
@@ -16776,7 +16764,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B584" s="2" t="n">
+      <c r="B584" s="1" t="n">
         <v>45449.76043981482</v>
       </c>
       <c r="C584" t="n">
@@ -16804,7 +16792,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B585" s="2" t="n">
+      <c r="B585" s="1" t="n">
         <v>45449.77085648148</v>
       </c>
       <c r="C585" t="n">
@@ -16832,7 +16820,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B586" s="2" t="n">
+      <c r="B586" s="1" t="n">
         <v>45449.78127314815</v>
       </c>
       <c r="C586" t="n">
@@ -16860,7 +16848,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B587" s="2" t="n">
+      <c r="B587" s="1" t="n">
         <v>45449.79167824074</v>
       </c>
       <c r="C587" t="n">
@@ -16888,7 +16876,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B588" s="2" t="n">
+      <c r="B588" s="1" t="n">
         <v>45449.80209490741</v>
       </c>
       <c r="C588" t="n">
@@ -16916,7 +16904,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B589" s="2" t="n">
+      <c r="B589" s="1" t="n">
         <v>45449.81251157408</v>
       </c>
       <c r="C589" t="n">
@@ -16944,7 +16932,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B590" s="2" t="n">
+      <c r="B590" s="1" t="n">
         <v>45449.82293981482</v>
       </c>
       <c r="C590" t="n">
@@ -16972,7 +16960,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B591" s="2" t="n">
+      <c r="B591" s="1" t="n">
         <v>45449.83335648148</v>
       </c>
       <c r="C591" t="n">
@@ -17000,7 +16988,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B592" s="2" t="n">
+      <c r="B592" s="1" t="n">
         <v>45449.84377314815</v>
       </c>
       <c r="C592" t="n">
@@ -17028,7 +17016,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B593" s="2" t="n">
+      <c r="B593" s="1" t="n">
         <v>45449.85417824074</v>
       </c>
       <c r="C593" t="n">
@@ -17056,7 +17044,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B594" s="2" t="n">
+      <c r="B594" s="1" t="n">
         <v>45449.86460648148</v>
       </c>
       <c r="C594" t="n">
@@ -17084,7 +17072,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B595" s="2" t="n">
+      <c r="B595" s="1" t="n">
         <v>45449.87501157408</v>
       </c>
       <c r="C595" t="n">
@@ -17112,7 +17100,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B596" s="2" t="n">
+      <c r="B596" s="1" t="n">
         <v>45449.88542824074</v>
       </c>
       <c r="C596" t="n">
@@ -17140,7 +17128,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B597" s="2" t="n">
+      <c r="B597" s="1" t="n">
         <v>45449.89585648148</v>
       </c>
       <c r="C597" t="n">
@@ -17168,7 +17156,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B598" s="2" t="n">
+      <c r="B598" s="1" t="n">
         <v>45449.90627314815</v>
       </c>
       <c r="C598" t="n">
@@ -17196,7 +17184,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B599" s="2" t="n">
+      <c r="B599" s="1" t="n">
         <v>45449.91667824074</v>
       </c>
       <c r="C599" t="n">
@@ -17224,7 +17212,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B600" s="2" t="n">
+      <c r="B600" s="1" t="n">
         <v>45449.92709490741</v>
       </c>
       <c r="C600" t="n">
@@ -17252,7 +17240,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B601" s="2" t="n">
+      <c r="B601" s="1" t="n">
         <v>45449.93751157408</v>
       </c>
       <c r="C601" t="n">
@@ -17280,7 +17268,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B602" s="2" t="n">
+      <c r="B602" s="1" t="n">
         <v>45449.94792824074</v>
       </c>
       <c r="C602" t="n">
@@ -17308,7 +17296,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B603" s="2" t="n">
+      <c r="B603" s="1" t="n">
         <v>45449.95835648148</v>
       </c>
       <c r="C603" t="n">
@@ -17336,7 +17324,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B604" s="2" t="n">
+      <c r="B604" s="1" t="n">
         <v>45449.96877314815</v>
       </c>
       <c r="C604" t="n">
@@ -17364,7 +17352,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B605" s="2" t="n">
+      <c r="B605" s="1" t="n">
         <v>45449.97917824074</v>
       </c>
       <c r="C605" t="n">
@@ -17392,7 +17380,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B606" s="2" t="n">
+      <c r="B606" s="1" t="n">
         <v>45449.98960648148</v>
       </c>
       <c r="C606" t="n">
@@ -17420,7 +17408,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B607" s="2" t="n">
+      <c r="B607" s="1" t="n">
         <v>45450.00002314815</v>
       </c>
       <c r="C607" t="n">
@@ -17448,7 +17436,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B608" s="2" t="n">
+      <c r="B608" s="1" t="n">
         <v>45450.01043981482</v>
       </c>
       <c r="C608" t="n">
@@ -17476,7 +17464,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B609" s="2" t="n">
+      <c r="B609" s="1" t="n">
         <v>45450.02084490741</v>
       </c>
       <c r="C609" t="n">
@@ -17504,7 +17492,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B610" s="2" t="n">
+      <c r="B610" s="1" t="n">
         <v>45450.03126157408</v>
       </c>
       <c r="C610" t="n">
@@ -17532,7 +17520,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B611" s="2" t="n">
+      <c r="B611" s="1" t="n">
         <v>45450.04167824074</v>
       </c>
       <c r="C611" t="n">
@@ -17560,7 +17548,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B612" s="2" t="n">
+      <c r="B612" s="1" t="n">
         <v>45450.05210648148</v>
       </c>
       <c r="C612" t="n">
@@ -17588,7 +17576,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B613" s="2" t="n">
+      <c r="B613" s="1" t="n">
         <v>45450.06252314815</v>
       </c>
       <c r="C613" t="n">
@@ -17616,7 +17604,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B614" s="2" t="n">
+      <c r="B614" s="1" t="n">
         <v>45450.07293981482</v>
       </c>
       <c r="C614" t="n">
@@ -17644,7 +17632,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B615" s="2" t="n">
+      <c r="B615" s="1" t="n">
         <v>45450.08335648148</v>
       </c>
       <c r="C615" t="n">
@@ -17672,7 +17660,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B616" s="2" t="n">
+      <c r="B616" s="1" t="n">
         <v>45450.09376157408</v>
       </c>
       <c r="C616" t="n">
@@ -17700,7 +17688,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B617" s="2" t="n">
+      <c r="B617" s="1" t="n">
         <v>45450.10417824074</v>
       </c>
       <c r="C617" t="n">
@@ -17728,7 +17716,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B618" s="2" t="n">
+      <c r="B618" s="1" t="n">
         <v>45450.11459490741</v>
       </c>
       <c r="C618" t="n">
@@ -17756,7 +17744,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B619" s="2" t="n">
+      <c r="B619" s="1" t="n">
         <v>45450.12502314815</v>
       </c>
       <c r="C619" t="n">
@@ -17784,7 +17772,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B620" s="2" t="n">
+      <c r="B620" s="1" t="n">
         <v>45450.13543981482</v>
       </c>
       <c r="C620" t="n">
@@ -17812,7 +17800,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B621" s="2" t="n">
+      <c r="B621" s="1" t="n">
         <v>45450.14585648148</v>
       </c>
       <c r="C621" t="n">
@@ -17840,7 +17828,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B622" s="2" t="n">
+      <c r="B622" s="1" t="n">
         <v>45450.15627314815</v>
       </c>
       <c r="C622" t="n">
@@ -17868,7 +17856,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B623" s="2" t="n">
+      <c r="B623" s="1" t="n">
         <v>45450.16667824074</v>
       </c>
       <c r="C623" t="n">
@@ -17896,7 +17884,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B624" s="2" t="n">
+      <c r="B624" s="1" t="n">
         <v>45450.17709490741</v>
       </c>
       <c r="C624" t="n">
@@ -17924,7 +17912,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B625" s="2" t="n">
+      <c r="B625" s="1" t="n">
         <v>45450.18751157408</v>
       </c>
       <c r="C625" t="n">
@@ -17952,7 +17940,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B626" s="2" t="n">
+      <c r="B626" s="1" t="n">
         <v>45450.19792824074</v>
       </c>
       <c r="C626" t="n">
@@ -17980,7 +17968,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B627" s="2" t="n">
+      <c r="B627" s="1" t="n">
         <v>45450.20834490741</v>
       </c>
       <c r="C627" t="n">
@@ -18008,7 +17996,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B628" s="2" t="n">
+      <c r="B628" s="1" t="n">
         <v>45450.21876157408</v>
       </c>
       <c r="C628" t="n">
@@ -18036,7 +18024,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B629" s="2" t="n">
+      <c r="B629" s="1" t="n">
         <v>45450.22917824074</v>
       </c>
       <c r="C629" t="n">
@@ -18064,7 +18052,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B630" s="2" t="n">
+      <c r="B630" s="1" t="n">
         <v>45450.23959490741</v>
       </c>
       <c r="C630" t="n">
@@ -18092,7 +18080,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B631" s="2" t="n">
+      <c r="B631" s="1" t="n">
         <v>45450.25001157408</v>
       </c>
       <c r="C631" t="n">
@@ -18120,7 +18108,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B632" s="2" t="n">
+      <c r="B632" s="1" t="n">
         <v>45450.26042824074</v>
       </c>
       <c r="C632" t="n">
@@ -18148,7 +18136,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B633" s="2" t="n">
+      <c r="B633" s="1" t="n">
         <v>45450.27084490741</v>
       </c>
       <c r="C633" t="n">
@@ -18176,7 +18164,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B634" s="2" t="n">
+      <c r="B634" s="1" t="n">
         <v>45450.28126157408</v>
       </c>
       <c r="C634" t="n">
@@ -18204,7 +18192,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B635" s="2" t="n">
+      <c r="B635" s="1" t="n">
         <v>45450.29167824074</v>
       </c>
       <c r="C635" t="n">
@@ -18232,7 +18220,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B636" s="2" t="n">
+      <c r="B636" s="1" t="n">
         <v>45450.30209490741</v>
       </c>
       <c r="C636" t="n">
@@ -18260,7 +18248,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B637" s="2" t="n">
+      <c r="B637" s="1" t="n">
         <v>45450.31251157408</v>
       </c>
       <c r="C637" t="n">
@@ -18288,7 +18276,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B638" s="2" t="n">
+      <c r="B638" s="1" t="n">
         <v>45450.32292824074</v>
       </c>
       <c r="C638" t="n">
@@ -18316,7 +18304,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B639" s="2" t="n">
+      <c r="B639" s="1" t="n">
         <v>45450.33334490741</v>
       </c>
       <c r="C639" t="n">
@@ -18344,7 +18332,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B640" s="2" t="n">
+      <c r="B640" s="1" t="n">
         <v>45450.34376157408</v>
       </c>
       <c r="C640" t="n">
@@ -18372,7 +18360,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B641" s="2" t="n">
+      <c r="B641" s="1" t="n">
         <v>45450.35417824074</v>
       </c>
       <c r="C641" t="n">
@@ -18400,7 +18388,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B642" s="2" t="n">
+      <c r="B642" s="1" t="n">
         <v>45450.36459490741</v>
       </c>
       <c r="C642" t="n">
@@ -18428,7 +18416,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B643" s="2" t="n">
+      <c r="B643" s="1" t="n">
         <v>45450.37501157408</v>
       </c>
       <c r="C643" t="n">
@@ -18456,7 +18444,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B644" s="2" t="n">
+      <c r="B644" s="1" t="n">
         <v>45450.38542824074</v>
       </c>
       <c r="C644" t="n">
@@ -18484,7 +18472,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B645" s="2" t="n">
+      <c r="B645" s="1" t="n">
         <v>45450.39584490741</v>
       </c>
       <c r="C645" t="n">
@@ -18512,7 +18500,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B646" s="2" t="n">
+      <c r="B646" s="1" t="n">
         <v>45450.40626157408</v>
       </c>
       <c r="C646" t="n">
@@ -18540,7 +18528,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B647" s="2" t="n">
+      <c r="B647" s="1" t="n">
         <v>45450.41667824074</v>
       </c>
       <c r="C647" t="n">
@@ -18568,7 +18556,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B648" s="2" t="n">
+      <c r="B648" s="1" t="n">
         <v>45450.42709490741</v>
       </c>
       <c r="C648" t="n">
@@ -18596,7 +18584,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B649" s="2" t="n">
+      <c r="B649" s="1" t="n">
         <v>45450.43751157408</v>
       </c>
       <c r="C649" t="n">
@@ -18624,7 +18612,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B650" s="2" t="n">
+      <c r="B650" s="1" t="n">
         <v>45450.44792824074</v>
       </c>
       <c r="C650" t="n">
@@ -18652,7 +18640,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B651" s="2" t="n">
+      <c r="B651" s="1" t="n">
         <v>45450.45834490741</v>
       </c>
       <c r="C651" t="n">
@@ -18680,7 +18668,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B652" s="2" t="n">
+      <c r="B652" s="1" t="n">
         <v>45450.46876157408</v>
       </c>
       <c r="C652" t="n">
@@ -18708,7 +18696,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B653" s="2" t="n">
+      <c r="B653" s="1" t="n">
         <v>45450.47917824074</v>
       </c>
       <c r="C653" t="n">
@@ -18736,7 +18724,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B654" s="2" t="n">
+      <c r="B654" s="1" t="n">
         <v>45450.48959490741</v>
       </c>
       <c r="C654" t="n">
@@ -18764,7 +18752,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B655" s="2" t="n">
+      <c r="B655" s="1" t="n">
         <v>45450.50001157408</v>
       </c>
       <c r="C655" t="n">
@@ -18792,7 +18780,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B656" s="2" t="n">
+      <c r="B656" s="1" t="n">
         <v>45450.51042824074</v>
       </c>
       <c r="C656" t="n">
@@ -18820,7 +18808,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B657" s="2" t="n">
+      <c r="B657" s="1" t="n">
         <v>45450.52084490741</v>
       </c>
       <c r="C657" t="n">
@@ -18848,7 +18836,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B658" s="2" t="n">
+      <c r="B658" s="1" t="n">
         <v>45450.53126157408</v>
       </c>
       <c r="C658" t="n">
@@ -18876,7 +18864,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B659" s="2" t="n">
+      <c r="B659" s="1" t="n">
         <v>45450.54167824074</v>
       </c>
       <c r="C659" t="n">
@@ -18904,7 +18892,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B660" s="2" t="n">
+      <c r="B660" s="1" t="n">
         <v>45450.55209490741</v>
       </c>
       <c r="C660" t="n">
@@ -18932,7 +18920,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B661" s="2" t="n">
+      <c r="B661" s="1" t="n">
         <v>45450.56251157408</v>
       </c>
       <c r="C661" t="n">
@@ -18960,7 +18948,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B662" s="2" t="n">
+      <c r="B662" s="1" t="n">
         <v>45450.57292824074</v>
       </c>
       <c r="C662" t="n">
@@ -18988,7 +18976,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B663" s="2" t="n">
+      <c r="B663" s="1" t="n">
         <v>45450.58334490741</v>
       </c>
       <c r="C663" t="n">
@@ -19016,7 +19004,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B664" s="2" t="n">
+      <c r="B664" s="1" t="n">
         <v>45450.59376157408</v>
       </c>
       <c r="C664" t="n">
@@ -19044,7 +19032,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B665" s="2" t="n">
+      <c r="B665" s="1" t="n">
         <v>45450.60417824074</v>
       </c>
       <c r="C665" t="n">
@@ -19072,7 +19060,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B666" s="2" t="n">
+      <c r="B666" s="1" t="n">
         <v>45450.61459490741</v>
       </c>
       <c r="C666" t="n">
@@ -19100,7 +19088,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B667" s="2" t="n">
+      <c r="B667" s="1" t="n">
         <v>45450.62501157408</v>
       </c>
       <c r="C667" t="n">
@@ -19128,7 +19116,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B668" s="2" t="n">
+      <c r="B668" s="1" t="n">
         <v>45450.63542824074</v>
       </c>
       <c r="C668" t="n">
@@ -19156,7 +19144,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B669" s="2" t="n">
+      <c r="B669" s="1" t="n">
         <v>45450.64584490741</v>
       </c>
       <c r="C669" t="n">
@@ -19184,7 +19172,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B670" s="2" t="n">
+      <c r="B670" s="1" t="n">
         <v>45450.65626157408</v>
       </c>
       <c r="C670" t="n">
@@ -19212,7 +19200,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B671" s="2" t="n">
+      <c r="B671" s="1" t="n">
         <v>45450.66667824074</v>
       </c>
       <c r="C671" t="n">
@@ -19240,7 +19228,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B672" s="2" t="n">
+      <c r="B672" s="1" t="n">
         <v>45450.67709490741</v>
       </c>
       <c r="C672" t="n">
@@ -19268,7 +19256,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B673" s="2" t="n">
+      <c r="B673" s="1" t="n">
         <v>45450.68751157408</v>
       </c>
       <c r="C673" t="n">
@@ -19296,7 +19284,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B674" s="2" t="n">
+      <c r="B674" s="1" t="n">
         <v>45450.69792824074</v>
       </c>
       <c r="C674" t="n">
@@ -19324,7 +19312,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B675" s="2" t="n">
+      <c r="B675" s="1" t="n">
         <v>45450.70834490741</v>
       </c>
       <c r="C675" t="n">
@@ -19352,7 +19340,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B676" s="2" t="n">
+      <c r="B676" s="1" t="n">
         <v>45450.71876157408</v>
       </c>
       <c r="C676" t="n">
@@ -19380,7 +19368,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B677" s="2" t="n">
+      <c r="B677" s="1" t="n">
         <v>45450.72917824074</v>
       </c>
       <c r="C677" t="n">
@@ -19408,7 +19396,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B678" s="2" t="n">
+      <c r="B678" s="1" t="n">
         <v>45450.73959490741</v>
       </c>
       <c r="C678" t="n">
@@ -19436,7 +19424,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B679" s="2" t="n">
+      <c r="B679" s="1" t="n">
         <v>45450.75001157408</v>
       </c>
       <c r="C679" t="n">
@@ -19464,7 +19452,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B680" s="2" t="n">
+      <c r="B680" s="1" t="n">
         <v>45450.76042824074</v>
       </c>
       <c r="C680" t="n">
@@ -19492,7 +19480,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B681" s="2" t="n">
+      <c r="B681" s="1" t="n">
         <v>45450.77084490741</v>
       </c>
       <c r="C681" t="n">
@@ -19520,7 +19508,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B682" s="2" t="n">
+      <c r="B682" s="1" t="n">
         <v>45450.78126157408</v>
       </c>
       <c r="C682" t="n">
@@ -19548,7 +19536,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B683" s="2" t="n">
+      <c r="B683" s="1" t="n">
         <v>45450.79167824074</v>
       </c>
       <c r="C683" t="n">
@@ -19576,7 +19564,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B684" s="2" t="n">
+      <c r="B684" s="1" t="n">
         <v>45450.80210648148</v>
       </c>
       <c r="C684" t="n">
@@ -19604,7 +19592,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B685" s="2" t="n">
+      <c r="B685" s="1" t="n">
         <v>45450.81252314815</v>
       </c>
       <c r="C685" t="n">
@@ -19632,7 +19620,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B686" s="2" t="n">
+      <c r="B686" s="1" t="n">
         <v>45450.82292824074</v>
       </c>
       <c r="C686" t="n">
@@ -19660,7 +19648,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B687" s="2" t="n">
+      <c r="B687" s="1" t="n">
         <v>45450.83334490741</v>
       </c>
       <c r="C687" t="n">
@@ -19688,7 +19676,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B688" s="2" t="n">
+      <c r="B688" s="1" t="n">
         <v>45450.84376157408</v>
       </c>
       <c r="C688" t="n">
@@ -19716,7 +19704,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B689" s="2" t="n">
+      <c r="B689" s="1" t="n">
         <v>45450.85417824074</v>
       </c>
       <c r="C689" t="n">
@@ -19744,7 +19732,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B690" s="2" t="n">
+      <c r="B690" s="1" t="n">
         <v>45450.86460648148</v>
       </c>
       <c r="C690" t="n">
@@ -19772,7 +19760,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B691" s="2" t="n">
+      <c r="B691" s="1" t="n">
         <v>45450.87501157408</v>
       </c>
       <c r="C691" t="n">
@@ -19800,7 +19788,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B692" s="2" t="n">
+      <c r="B692" s="1" t="n">
         <v>45450.88543981482</v>
       </c>
       <c r="C692" t="n">
@@ -19828,7 +19816,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B693" s="2" t="n">
+      <c r="B693" s="1" t="n">
         <v>45450.89585648148</v>
       </c>
       <c r="C693" t="n">
@@ -19856,7 +19844,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B694" s="2" t="n">
+      <c r="B694" s="1" t="n">
         <v>45450.90627314815</v>
       </c>
       <c r="C694" t="n">
@@ -19884,7 +19872,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B695" s="2" t="n">
+      <c r="B695" s="1" t="n">
         <v>45450.91668981482</v>
       </c>
       <c r="C695" t="n">
@@ -19912,7 +19900,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B696" s="2" t="n">
+      <c r="B696" s="1" t="n">
         <v>45450.92709490741</v>
       </c>
       <c r="C696" t="n">
@@ -19940,7 +19928,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B697" s="2" t="n">
+      <c r="B697" s="1" t="n">
         <v>45450.93751157408</v>
       </c>
       <c r="C697" t="n">
@@ -19968,7 +19956,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B698" s="2" t="n">
+      <c r="B698" s="1" t="n">
         <v>45450.94792824074</v>
       </c>
       <c r="C698" t="n">
@@ -19996,7 +19984,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B699" s="2" t="n">
+      <c r="B699" s="1" t="n">
         <v>45450.95835648148</v>
       </c>
       <c r="C699" t="n">
@@ -20024,7 +20012,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B700" s="2" t="n">
+      <c r="B700" s="1" t="n">
         <v>45450.96877314815</v>
       </c>
       <c r="C700" t="n">
@@ -20052,7 +20040,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B701" s="2" t="n">
+      <c r="B701" s="1" t="n">
         <v>45450.97918981482</v>
       </c>
       <c r="C701" t="n">
@@ -20080,7 +20068,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B702" s="2" t="n">
+      <c r="B702" s="1" t="n">
         <v>45450.98960648148</v>
       </c>
       <c r="C702" t="n">
@@ -20108,7 +20096,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B703" s="2" t="n">
+      <c r="B703" s="1" t="n">
         <v>45451.00001157408</v>
       </c>
       <c r="C703" t="n">
@@ -20136,7 +20124,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B704" s="2" t="n">
+      <c r="B704" s="1" t="n">
         <v>45451.01042824074</v>
       </c>
       <c r="C704" t="n">
@@ -20164,7 +20152,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B705" s="2" t="n">
+      <c r="B705" s="1" t="n">
         <v>45451.02084490741</v>
       </c>
       <c r="C705" t="n">
@@ -20192,7 +20180,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B706" s="2" t="n">
+      <c r="B706" s="1" t="n">
         <v>45451.03126157408</v>
       </c>
       <c r="C706" t="n">
@@ -20220,7 +20208,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B707" s="2" t="n">
+      <c r="B707" s="1" t="n">
         <v>45451.04168981482</v>
       </c>
       <c r="C707" t="n">
@@ -20248,7 +20236,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B708" s="2" t="n">
+      <c r="B708" s="1" t="n">
         <v>45451.05210648148</v>
       </c>
       <c r="C708" t="n">
@@ -20276,7 +20264,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B709" s="2" t="n">
+      <c r="B709" s="1" t="n">
         <v>45451.06252314815</v>
       </c>
       <c r="C709" t="n">
@@ -20304,7 +20292,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B710" s="2" t="n">
+      <c r="B710" s="1" t="n">
         <v>45451.07292824074</v>
       </c>
       <c r="C710" t="n">
@@ -20332,7 +20320,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B711" s="2" t="n">
+      <c r="B711" s="1" t="n">
         <v>45451.08334490741</v>
       </c>
       <c r="C711" t="n">
@@ -20360,7 +20348,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B712" s="2" t="n">
+      <c r="B712" s="1" t="n">
         <v>45451.09376157408</v>
       </c>
       <c r="C712" t="n">
@@ -20388,7 +20376,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B713" s="2" t="n">
+      <c r="B713" s="1" t="n">
         <v>45451.10418981482</v>
       </c>
       <c r="C713" t="n">
@@ -20416,7 +20404,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B714" s="2" t="n">
+      <c r="B714" s="1" t="n">
         <v>45451.11460648148</v>
       </c>
       <c r="C714" t="n">
@@ -20444,7 +20432,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B715" s="2" t="n">
+      <c r="B715" s="1" t="n">
         <v>45451.12501157408</v>
       </c>
       <c r="C715" t="n">
@@ -20472,7 +20460,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B716" s="2" t="n">
+      <c r="B716" s="1" t="n">
         <v>45451.13542824074</v>
       </c>
       <c r="C716" t="n">
@@ -20500,7 +20488,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B717" s="2" t="n">
+      <c r="B717" s="1" t="n">
         <v>45451.14584490741</v>
       </c>
       <c r="C717" t="n">
@@ -20528,7 +20516,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B718" s="2" t="n">
+      <c r="B718" s="1" t="n">
         <v>45451.15626157408</v>
       </c>
       <c r="C718" t="n">
@@ -20556,7 +20544,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B719" s="2" t="n">
+      <c r="B719" s="1" t="n">
         <v>45451.16668981482</v>
       </c>
       <c r="C719" t="n">
@@ -20584,7 +20572,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B720" s="2" t="n">
+      <c r="B720" s="1" t="n">
         <v>45451.17709490741</v>
       </c>
       <c r="C720" t="n">
@@ -20612,7 +20600,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B721" s="2" t="n">
+      <c r="B721" s="1" t="n">
         <v>45451.18752314815</v>
       </c>
       <c r="C721" t="n">
@@ -20640,7 +20628,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B722" s="2" t="n">
+      <c r="B722" s="1" t="n">
         <v>45451.19793981482</v>
       </c>
       <c r="C722" t="n">
@@ -20668,7 +20656,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B723" s="2" t="n">
+      <c r="B723" s="1" t="n">
         <v>45451.20835648148</v>
       </c>
       <c r="C723" t="n">
@@ -20696,7 +20684,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B724" s="2" t="n">
+      <c r="B724" s="1" t="n">
         <v>45451.21877314815</v>
       </c>
       <c r="C724" t="n">
@@ -20724,7 +20712,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B725" s="2" t="n">
+      <c r="B725" s="1" t="n">
         <v>45451.22918981482</v>
       </c>
       <c r="C725" t="n">
@@ -20752,7 +20740,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B726" s="2" t="n">
+      <c r="B726" s="1" t="n">
         <v>45451.23960648148</v>
       </c>
       <c r="C726" t="n">
@@ -20780,7 +20768,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B727" s="2" t="n">
+      <c r="B727" s="1" t="n">
         <v>45451.25001157408</v>
       </c>
       <c r="C727" t="n">
@@ -20808,7 +20796,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B728" s="2" t="n">
+      <c r="B728" s="1" t="n">
         <v>45451.26042824074</v>
       </c>
       <c r="C728" t="n">
@@ -20836,7 +20824,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B729" s="2" t="n">
+      <c r="B729" s="1" t="n">
         <v>45451.27084490741</v>
       </c>
       <c r="C729" t="n">
@@ -20864,7 +20852,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B730" s="2" t="n">
+      <c r="B730" s="1" t="n">
         <v>45451.28126157408</v>
       </c>
       <c r="C730" t="n">
@@ -20892,7 +20880,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B731" s="2" t="n">
+      <c r="B731" s="1" t="n">
         <v>45451.29167824074</v>
       </c>
       <c r="C731" t="n">
@@ -20920,7 +20908,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B732" s="2" t="n">
+      <c r="B732" s="1" t="n">
         <v>45451.30209490741</v>
       </c>
       <c r="C732" t="n">
@@ -20948,7 +20936,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B733" s="2" t="n">
+      <c r="B733" s="1" t="n">
         <v>45451.31251157408</v>
       </c>
       <c r="C733" t="n">
@@ -20976,7 +20964,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B734" s="2" t="n">
+      <c r="B734" s="1" t="n">
         <v>45451.32292824074</v>
       </c>
       <c r="C734" t="n">
@@ -21004,7 +20992,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B735" s="2" t="n">
+      <c r="B735" s="1" t="n">
         <v>45451.33334490741</v>
       </c>
       <c r="C735" t="n">
@@ -21032,7 +21020,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B736" s="2" t="n">
+      <c r="B736" s="1" t="n">
         <v>45451.34376157408</v>
       </c>
       <c r="C736" t="n">
@@ -21060,7 +21048,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B737" s="2" t="n">
+      <c r="B737" s="1" t="n">
         <v>45451.35417824074</v>
       </c>
       <c r="C737" t="n">
@@ -21088,7 +21076,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B738" s="2" t="n">
+      <c r="B738" s="1" t="n">
         <v>45451.36459490741</v>
       </c>
       <c r="C738" t="n">
@@ -21116,7 +21104,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B739" s="2" t="n">
+      <c r="B739" s="1" t="n">
         <v>45451.37501157408</v>
       </c>
       <c r="C739" t="n">
@@ -21144,7 +21132,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B740" s="2" t="n">
+      <c r="B740" s="1" t="n">
         <v>45451.38542824074</v>
       </c>
       <c r="C740" t="n">
@@ -21172,7 +21160,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B741" s="2" t="n">
+      <c r="B741" s="1" t="n">
         <v>45451.39584490741</v>
       </c>
       <c r="C741" t="n">
@@ -21200,7 +21188,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B742" s="2" t="n">
+      <c r="B742" s="1" t="n">
         <v>45451.40626157408</v>
       </c>
       <c r="C742" t="n">
@@ -21228,7 +21216,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B743" s="2" t="n">
+      <c r="B743" s="1" t="n">
         <v>45451.41667824074</v>
       </c>
       <c r="C743" t="n">
@@ -21256,7 +21244,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B744" s="2" t="n">
+      <c r="B744" s="1" t="n">
         <v>45451.42709490741</v>
       </c>
       <c r="C744" t="n">
@@ -21284,7 +21272,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B745" s="2" t="n">
+      <c r="B745" s="1" t="n">
         <v>45451.43751157408</v>
       </c>
       <c r="C745" t="n">
@@ -21312,7 +21300,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B746" s="2" t="n">
+      <c r="B746" s="1" t="n">
         <v>45451.44792824074</v>
       </c>
       <c r="C746" t="n">
@@ -21340,7 +21328,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B747" s="2" t="n">
+      <c r="B747" s="1" t="n">
         <v>45451.45834490741</v>
       </c>
       <c r="C747" t="n">
@@ -21368,7 +21356,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B748" s="2" t="n">
+      <c r="B748" s="1" t="n">
         <v>45451.46876157408</v>
       </c>
       <c r="C748" t="n">
@@ -21396,7 +21384,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B749" s="2" t="n">
+      <c r="B749" s="1" t="n">
         <v>45451.47917824074</v>
       </c>
       <c r="C749" t="n">
@@ -21424,7 +21412,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B750" s="2" t="n">
+      <c r="B750" s="1" t="n">
         <v>45451.48959490741</v>
       </c>
       <c r="C750" t="n">
@@ -21452,7 +21440,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B751" s="2" t="n">
+      <c r="B751" s="1" t="n">
         <v>45451.50001157408</v>
       </c>
       <c r="C751" t="n">
@@ -21480,7 +21468,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B752" s="2" t="n">
+      <c r="B752" s="1" t="n">
         <v>45451.51042824074</v>
       </c>
       <c r="C752" t="n">
@@ -21508,7 +21496,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B753" s="2" t="n">
+      <c r="B753" s="1" t="n">
         <v>45451.52084490741</v>
       </c>
       <c r="C753" t="n">
@@ -21536,7 +21524,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B754" s="2" t="n">
+      <c r="B754" s="1" t="n">
         <v>45451.53126157408</v>
       </c>
       <c r="C754" t="n">
@@ -21564,7 +21552,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B755" s="2" t="n">
+      <c r="B755" s="1" t="n">
         <v>45451.54167824074</v>
       </c>
       <c r="C755" t="n">
@@ -21592,7 +21580,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B756" s="2" t="n">
+      <c r="B756" s="1" t="n">
         <v>45451.55209490741</v>
       </c>
       <c r="C756" t="n">
@@ -21620,7 +21608,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B757" s="2" t="n">
+      <c r="B757" s="1" t="n">
         <v>45451.56251157408</v>
       </c>
       <c r="C757" t="n">
@@ -21648,7 +21636,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B758" s="2" t="n">
+      <c r="B758" s="1" t="n">
         <v>45451.57292824074</v>
       </c>
       <c r="C758" t="n">
@@ -21676,7 +21664,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B759" s="2" t="n">
+      <c r="B759" s="1" t="n">
         <v>45451.58334490741</v>
       </c>
       <c r="C759" t="n">
@@ -21704,7 +21692,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B760" s="2" t="n">
+      <c r="B760" s="1" t="n">
         <v>45451.59376157408</v>
       </c>
       <c r="C760" t="n">
@@ -21732,7 +21720,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B761" s="2" t="n">
+      <c r="B761" s="1" t="n">
         <v>45451.60417824074</v>
       </c>
       <c r="C761" t="n">
@@ -21760,7 +21748,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B762" s="2" t="n">
+      <c r="B762" s="1" t="n">
         <v>45451.61459490741</v>
       </c>
       <c r="C762" t="n">
@@ -21788,7 +21776,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B763" s="2" t="n">
+      <c r="B763" s="1" t="n">
         <v>45451.62501157408</v>
       </c>
       <c r="C763" t="n">
@@ -21816,7 +21804,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B764" s="2" t="n">
+      <c r="B764" s="1" t="n">
         <v>45451.63542824074</v>
       </c>
       <c r="C764" t="n">
@@ -21844,7 +21832,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B765" s="2" t="n">
+      <c r="B765" s="1" t="n">
         <v>45451.64584490741</v>
       </c>
       <c r="C765" t="n">
@@ -21872,7 +21860,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B766" s="2" t="n">
+      <c r="B766" s="1" t="n">
         <v>45451.65626157408</v>
       </c>
       <c r="C766" t="n">
@@ -21900,7 +21888,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B767" s="2" t="n">
+      <c r="B767" s="1" t="n">
         <v>45451.66667824074</v>
       </c>
       <c r="C767" t="n">
@@ -21928,7 +21916,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B768" s="2" t="n">
+      <c r="B768" s="1" t="n">
         <v>45451.67709490741</v>
       </c>
       <c r="C768" t="n">
@@ -21956,7 +21944,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B769" s="2" t="n">
+      <c r="B769" s="1" t="n">
         <v>45451.68751157408</v>
       </c>
       <c r="C769" t="n">
@@ -21984,7 +21972,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B770" s="2" t="n">
+      <c r="B770" s="1" t="n">
         <v>45451.69792824074</v>
       </c>
       <c r="C770" t="n">
@@ -22012,7 +22000,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B771" s="2" t="n">
+      <c r="B771" s="1" t="n">
         <v>45451.70834490741</v>
       </c>
       <c r="C771" t="n">
@@ -22040,7 +22028,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B772" s="2" t="n">
+      <c r="B772" s="1" t="n">
         <v>45451.71876157408</v>
       </c>
       <c r="C772" t="n">
@@ -22068,7 +22056,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B773" s="2" t="n">
+      <c r="B773" s="1" t="n">
         <v>45451.72917824074</v>
       </c>
       <c r="C773" t="n">
@@ -22096,7 +22084,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B774" s="2" t="n">
+      <c r="B774" s="1" t="n">
         <v>45451.73959490741</v>
       </c>
       <c r="C774" t="n">
@@ -22124,7 +22112,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B775" s="2" t="n">
+      <c r="B775" s="1" t="n">
         <v>45451.75001157408</v>
       </c>
       <c r="C775" t="n">
@@ -22152,7 +22140,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B776" s="2" t="n">
+      <c r="B776" s="1" t="n">
         <v>45451.76043981482</v>
       </c>
       <c r="C776" t="n">
@@ -22180,7 +22168,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B777" s="2" t="n">
+      <c r="B777" s="1" t="n">
         <v>45451.77085648148</v>
       </c>
       <c r="C777" t="n">
@@ -22208,7 +22196,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B778" s="2" t="n">
+      <c r="B778" s="1" t="n">
         <v>45451.78127314815</v>
       </c>
       <c r="C778" t="n">
@@ -22236,7 +22224,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B779" s="2" t="n">
+      <c r="B779" s="1" t="n">
         <v>45451.79168981482</v>
       </c>
       <c r="C779" t="n">
@@ -22264,7 +22252,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B780" s="2" t="n">
+      <c r="B780" s="1" t="n">
         <v>45451.80209490741</v>
       </c>
       <c r="C780" t="n">
@@ -22292,7 +22280,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B781" s="2" t="n">
+      <c r="B781" s="1" t="n">
         <v>45451.81251157408</v>
       </c>
       <c r="C781" t="n">
@@ -22320,7 +22308,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B782" s="2" t="n">
+      <c r="B782" s="1" t="n">
         <v>45451.82292824074</v>
       </c>
       <c r="C782" t="n">
@@ -22348,7 +22336,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B783" s="2" t="n">
+      <c r="B783" s="1" t="n">
         <v>45451.83334490741</v>
       </c>
       <c r="C783" t="n">
@@ -22376,7 +22364,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B784" s="2" t="n">
+      <c r="B784" s="1" t="n">
         <v>45451.84376157408</v>
       </c>
       <c r="C784" t="n">
@@ -22404,7 +22392,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B785" s="2" t="n">
+      <c r="B785" s="1" t="n">
         <v>45451.85418981482</v>
       </c>
       <c r="C785" t="n">
@@ -22432,7 +22420,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B786" s="2" t="n">
+      <c r="B786" s="1" t="n">
         <v>45451.86460648148</v>
       </c>
       <c r="C786" t="n">
@@ -22460,7 +22448,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B787" s="2" t="n">
+      <c r="B787" s="1" t="n">
         <v>45451.87502314815</v>
       </c>
       <c r="C787" t="n">
@@ -22488,7 +22476,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B788" s="2" t="n">
+      <c r="B788" s="1" t="n">
         <v>45451.88542824074</v>
       </c>
       <c r="C788" t="n">
@@ -22516,7 +22504,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B789" s="2" t="n">
+      <c r="B789" s="1" t="n">
         <v>45451.89584490741</v>
       </c>
       <c r="C789" t="n">
@@ -22544,7 +22532,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B790" s="2" t="n">
+      <c r="B790" s="1" t="n">
         <v>45451.90626157408</v>
       </c>
       <c r="C790" t="n">
@@ -22572,7 +22560,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B791" s="2" t="n">
+      <c r="B791" s="1" t="n">
         <v>45451.91667824074</v>
       </c>
       <c r="C791" t="n">
@@ -22600,7 +22588,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B792" s="2" t="n">
+      <c r="B792" s="1" t="n">
         <v>45451.92709490741</v>
       </c>
       <c r="C792" t="n">
@@ -22628,7 +22616,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B793" s="2" t="n">
+      <c r="B793" s="1" t="n">
         <v>45451.93751157408</v>
       </c>
       <c r="C793" t="n">
@@ -22656,7 +22644,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B794" s="2" t="n">
+      <c r="B794" s="1" t="n">
         <v>45451.94792824074</v>
       </c>
       <c r="C794" t="n">
@@ -22684,7 +22672,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B795" s="2" t="n">
+      <c r="B795" s="1" t="n">
         <v>45451.95834490741</v>
       </c>
       <c r="C795" t="n">
@@ -22712,7 +22700,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B796" s="2" t="n">
+      <c r="B796" s="1" t="n">
         <v>45451.96876157408</v>
       </c>
       <c r="C796" t="n">
@@ -22740,7 +22728,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B797" s="2" t="n">
+      <c r="B797" s="1" t="n">
         <v>45451.97917824074</v>
       </c>
       <c r="C797" t="n">
@@ -22768,7 +22756,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B798" s="2" t="n">
+      <c r="B798" s="1" t="n">
         <v>45451.98959490741</v>
       </c>
       <c r="C798" t="n">
@@ -22796,7 +22784,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B799" s="2" t="n">
+      <c r="B799" s="1" t="n">
         <v>45452.00001157408</v>
       </c>
       <c r="C799" t="n">
@@ -22824,7 +22812,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B800" s="2" t="n">
+      <c r="B800" s="1" t="n">
         <v>45452.01042824074</v>
       </c>
       <c r="C800" t="n">
@@ -22852,7 +22840,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B801" s="2" t="n">
+      <c r="B801" s="1" t="n">
         <v>45452.02084490741</v>
       </c>
       <c r="C801" t="n">
@@ -22880,7 +22868,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B802" s="2" t="n">
+      <c r="B802" s="1" t="n">
         <v>45452.03126157408</v>
       </c>
       <c r="C802" t="n">
@@ -22908,7 +22896,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B803" s="2" t="n">
+      <c r="B803" s="1" t="n">
         <v>45452.04167824074</v>
       </c>
       <c r="C803" t="n">
@@ -22936,7 +22924,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B804" s="2" t="n">
+      <c r="B804" s="1" t="n">
         <v>45452.05209490741</v>
       </c>
       <c r="C804" t="n">
@@ -22964,7 +22952,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B805" s="2" t="n">
+      <c r="B805" s="1" t="n">
         <v>45452.06251157408</v>
       </c>
       <c r="C805" t="n">
@@ -22992,7 +22980,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B806" s="2" t="n">
+      <c r="B806" s="1" t="n">
         <v>45452.07292824074</v>
       </c>
       <c r="C806" t="n">
@@ -23020,7 +23008,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B807" s="2" t="n">
+      <c r="B807" s="1" t="n">
         <v>45452.08334490741</v>
       </c>
       <c r="C807" t="n">
@@ -23048,7 +23036,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B808" s="2" t="n">
+      <c r="B808" s="1" t="n">
         <v>45452.09376157408</v>
       </c>
       <c r="C808" t="n">
@@ -23076,7 +23064,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B809" s="2" t="n">
+      <c r="B809" s="1" t="n">
         <v>45452.10417824074</v>
       </c>
       <c r="C809" t="n">
@@ -23104,7 +23092,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B810" s="2" t="n">
+      <c r="B810" s="1" t="n">
         <v>45452.11459490741</v>
       </c>
       <c r="C810" t="n">
@@ -23132,7 +23120,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B811" s="2" t="n">
+      <c r="B811" s="1" t="n">
         <v>45452.12501157408</v>
       </c>
       <c r="C811" t="n">
@@ -23160,7 +23148,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B812" s="2" t="n">
+      <c r="B812" s="1" t="n">
         <v>45452.13542824074</v>
       </c>
       <c r="C812" t="n">
@@ -23188,7 +23176,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B813" s="2" t="n">
+      <c r="B813" s="1" t="n">
         <v>45452.14584490741</v>
       </c>
       <c r="C813" t="n">
@@ -23216,7 +23204,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B814" s="2" t="n">
+      <c r="B814" s="1" t="n">
         <v>45452.15626157408</v>
       </c>
       <c r="C814" t="n">
@@ -23244,7 +23232,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B815" s="2" t="n">
+      <c r="B815" s="1" t="n">
         <v>45452.16667824074</v>
       </c>
       <c r="C815" t="n">
@@ -23272,7 +23260,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B816" s="2" t="n">
+      <c r="B816" s="1" t="n">
         <v>45452.17709490741</v>
       </c>
       <c r="C816" t="n">
@@ -23300,7 +23288,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B817" s="2" t="n">
+      <c r="B817" s="1" t="n">
         <v>45452.18751157408</v>
       </c>
       <c r="C817" t="n">
@@ -23328,7 +23316,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B818" s="2" t="n">
+      <c r="B818" s="1" t="n">
         <v>45452.19793981482</v>
       </c>
       <c r="C818" t="n">
@@ -23356,7 +23344,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B819" s="2" t="n">
+      <c r="B819" s="1" t="n">
         <v>45452.20835648148</v>
       </c>
       <c r="C819" t="n">
@@ -23384,7 +23372,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B820" s="2" t="n">
+      <c r="B820" s="1" t="n">
         <v>45452.21877314815</v>
       </c>
       <c r="C820" t="n">
@@ -23412,7 +23400,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B821" s="2" t="n">
+      <c r="B821" s="1" t="n">
         <v>45452.22917824074</v>
       </c>
       <c r="C821" t="n">
@@ -23440,7 +23428,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B822" s="2" t="n">
+      <c r="B822" s="1" t="n">
         <v>45452.23959490741</v>
       </c>
       <c r="C822" t="n">
@@ -23468,7 +23456,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B823" s="2" t="n">
+      <c r="B823" s="1" t="n">
         <v>45452.25001157408</v>
       </c>
       <c r="C823" t="n">
@@ -23496,7 +23484,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B824" s="2" t="n">
+      <c r="B824" s="1" t="n">
         <v>45452.26043981482</v>
       </c>
       <c r="C824" t="n">
@@ -23524,7 +23512,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B825" s="2" t="n">
+      <c r="B825" s="1" t="n">
         <v>45452.27084490741</v>
       </c>
       <c r="C825" t="n">
@@ -23552,7 +23540,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B826" s="2" t="n">
+      <c r="B826" s="1" t="n">
         <v>45452.28126157408</v>
       </c>
       <c r="C826" t="n">
@@ -23580,7 +23568,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B827" s="2" t="n">
+      <c r="B827" s="1" t="n">
         <v>45452.29167824074</v>
       </c>
       <c r="C827" t="n">
@@ -23608,7 +23596,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B828" s="2" t="n">
+      <c r="B828" s="1" t="n">
         <v>45452.30210648148</v>
       </c>
       <c r="C828" t="n">
@@ -23636,7 +23624,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B829" s="2" t="n">
+      <c r="B829" s="1" t="n">
         <v>45452.31252314815</v>
       </c>
       <c r="C829" t="n">
@@ -23664,7 +23652,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B830" s="2" t="n">
+      <c r="B830" s="1" t="n">
         <v>45452.32292824074</v>
       </c>
       <c r="C830" t="n">
@@ -23692,7 +23680,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B831" s="2" t="n">
+      <c r="B831" s="1" t="n">
         <v>45452.33334490741</v>
       </c>
       <c r="C831" t="n">
@@ -23720,7 +23708,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B832" s="2" t="n">
+      <c r="B832" s="1" t="n">
         <v>45452.34376157408</v>
       </c>
       <c r="C832" t="n">
@@ -23748,7 +23736,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B833" s="2" t="n">
+      <c r="B833" s="1" t="n">
         <v>45452.35417824074</v>
       </c>
       <c r="C833" t="n">
@@ -23776,7 +23764,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B834" s="2" t="n">
+      <c r="B834" s="1" t="n">
         <v>45452.36459490741</v>
       </c>
       <c r="C834" t="n">
@@ -23804,7 +23792,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B835" s="2" t="n">
+      <c r="B835" s="1" t="n">
         <v>45452.37502314815</v>
       </c>
       <c r="C835" t="n">
@@ -23832,7 +23820,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B836" s="2" t="n">
+      <c r="B836" s="1" t="n">
         <v>45452.38543981482</v>
       </c>
       <c r="C836" t="n">
@@ -23860,7 +23848,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B837" s="2" t="n">
+      <c r="B837" s="1" t="n">
         <v>45452.39584490741</v>
       </c>
       <c r="C837" t="n">
@@ -23888,7 +23876,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B838" s="2" t="n">
+      <c r="B838" s="1" t="n">
         <v>45452.40626157408</v>
       </c>
       <c r="C838" t="n">
@@ -23916,7 +23904,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B839" s="2" t="n">
+      <c r="B839" s="1" t="n">
         <v>45452.41667824074</v>
       </c>
       <c r="C839" t="n">
@@ -23944,7 +23932,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B840" s="2" t="n">
+      <c r="B840" s="1" t="n">
         <v>45452.42709490741</v>
       </c>
       <c r="C840" t="n">
@@ -23972,7 +23960,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B841" s="2" t="n">
+      <c r="B841" s="1" t="n">
         <v>45452.43751157408</v>
       </c>
       <c r="C841" t="n">
@@ -24000,7 +23988,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B842" s="2" t="n">
+      <c r="B842" s="1" t="n">
         <v>45452.44792824074</v>
       </c>
       <c r="C842" t="n">
@@ -24028,7 +24016,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B843" s="2" t="n">
+      <c r="B843" s="1" t="n">
         <v>45452.45834490741</v>
       </c>
       <c r="C843" t="n">
@@ -24056,7 +24044,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B844" s="2" t="n">
+      <c r="B844" s="1" t="n">
         <v>45452.46876157408</v>
       </c>
       <c r="C844" t="n">
@@ -24084,7 +24072,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B845" s="2" t="n">
+      <c r="B845" s="1" t="n">
         <v>45452.47917824074</v>
       </c>
       <c r="C845" t="n">
@@ -24112,7 +24100,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B846" s="2" t="n">
+      <c r="B846" s="1" t="n">
         <v>45452.48959490741</v>
       </c>
       <c r="C846" t="n">
@@ -24140,7 +24128,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B847" s="2" t="n">
+      <c r="B847" s="1" t="n">
         <v>45452.50001157408</v>
       </c>
       <c r="C847" t="n">
@@ -24168,7 +24156,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B848" s="2" t="n">
+      <c r="B848" s="1" t="n">
         <v>45452.51042824074</v>
       </c>
       <c r="C848" t="n">
@@ -24196,7 +24184,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B849" s="2" t="n">
+      <c r="B849" s="1" t="n">
         <v>45452.52084490741</v>
       </c>
       <c r="C849" t="n">
@@ -24224,7 +24212,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B850" s="2" t="n">
+      <c r="B850" s="1" t="n">
         <v>45452.53126157408</v>
       </c>
       <c r="C850" t="n">
@@ -24252,7 +24240,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B851" s="2" t="n">
+      <c r="B851" s="1" t="n">
         <v>45452.54167824074</v>
       </c>
       <c r="C851" t="n">
@@ -24280,7 +24268,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B852" s="2" t="n">
+      <c r="B852" s="1" t="n">
         <v>45452.55209490741</v>
       </c>
       <c r="C852" t="n">
@@ -24308,7 +24296,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B853" s="2" t="n">
+      <c r="B853" s="1" t="n">
         <v>45452.56251157408</v>
       </c>
       <c r="C853" t="n">
@@ -24336,7 +24324,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B854" s="2" t="n">
+      <c r="B854" s="1" t="n">
         <v>45452.57292824074</v>
       </c>
       <c r="C854" t="n">
@@ -24364,7 +24352,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B855" s="2" t="n">
+      <c r="B855" s="1" t="n">
         <v>45452.58334490741</v>
       </c>
       <c r="C855" t="n">
@@ -24392,7 +24380,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B856" s="2" t="n">
+      <c r="B856" s="1" t="n">
         <v>45452.59376157408</v>
       </c>
       <c r="C856" t="n">
@@ -24420,7 +24408,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B857" s="2" t="n">
+      <c r="B857" s="1" t="n">
         <v>45452.60417824074</v>
       </c>
       <c r="C857" t="n">
@@ -24448,7 +24436,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B858" s="2" t="n">
+      <c r="B858" s="1" t="n">
         <v>45452.61459490741</v>
       </c>
       <c r="C858" t="n">
@@ -24476,7 +24464,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B859" s="2" t="n">
+      <c r="B859" s="1" t="n">
         <v>45452.62501157408</v>
       </c>
       <c r="C859" t="n">
@@ -24504,7 +24492,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B860" s="2" t="n">
+      <c r="B860" s="1" t="n">
         <v>45452.63542824074</v>
       </c>
       <c r="C860" t="n">
@@ -24532,7 +24520,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B861" s="2" t="n">
+      <c r="B861" s="1" t="n">
         <v>45452.64584490741</v>
       </c>
       <c r="C861" t="n">
@@ -24560,7 +24548,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B862" s="2" t="n">
+      <c r="B862" s="1" t="n">
         <v>45452.65626157408</v>
       </c>
       <c r="C862" t="n">
@@ -24588,7 +24576,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B863" s="2" t="n">
+      <c r="B863" s="1" t="n">
         <v>45452.66667824074</v>
       </c>
       <c r="C863" t="n">
@@ -24616,7 +24604,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B864" s="2" t="n">
+      <c r="B864" s="1" t="n">
         <v>45452.67709490741</v>
       </c>
       <c r="C864" t="n">
@@ -24644,7 +24632,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B865" s="2" t="n">
+      <c r="B865" s="1" t="n">
         <v>45452.68751157408</v>
       </c>
       <c r="C865" t="n">
@@ -24672,7 +24660,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B866" s="2" t="n">
+      <c r="B866" s="1" t="n">
         <v>45452.69792824074</v>
       </c>
       <c r="C866" t="n">
@@ -24700,7 +24688,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B867" s="2" t="n">
+      <c r="B867" s="1" t="n">
         <v>45452.70834490741</v>
       </c>
       <c r="C867" t="n">
@@ -24728,7 +24716,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B868" s="2" t="n">
+      <c r="B868" s="1" t="n">
         <v>45452.71876157408</v>
       </c>
       <c r="C868" t="n">
@@ -24756,7 +24744,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B869" s="2" t="n">
+      <c r="B869" s="1" t="n">
         <v>45452.72917824074</v>
       </c>
       <c r="C869" t="n">
@@ -24784,7 +24772,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B870" s="2" t="n">
+      <c r="B870" s="1" t="n">
         <v>45452.73959490741</v>
       </c>
       <c r="C870" t="n">
@@ -24812,7 +24800,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B871" s="2" t="n">
+      <c r="B871" s="1" t="n">
         <v>45452.75001157408</v>
       </c>
       <c r="C871" t="n">
@@ -24840,7 +24828,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B872" s="2" t="n">
+      <c r="B872" s="1" t="n">
         <v>45452.76042824074</v>
       </c>
       <c r="C872" t="n">
@@ -24868,7 +24856,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B873" s="2" t="n">
+      <c r="B873" s="1" t="n">
         <v>45452.77084490741</v>
       </c>
       <c r="C873" t="n">
@@ -24896,7 +24884,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B874" s="2" t="n">
+      <c r="B874" s="1" t="n">
         <v>45452.78126157408</v>
       </c>
       <c r="C874" t="n">
@@ -24924,7 +24912,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B875" s="2" t="n">
+      <c r="B875" s="1" t="n">
         <v>45452.79167824074</v>
       </c>
       <c r="C875" t="n">
@@ -24952,7 +24940,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B876" s="2" t="n">
+      <c r="B876" s="1" t="n">
         <v>45452.80209490741</v>
       </c>
       <c r="C876" t="n">
@@ -24980,7 +24968,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B877" s="2" t="n">
+      <c r="B877" s="1" t="n">
         <v>45452.81251157408</v>
       </c>
       <c r="C877" t="n">
@@ -25008,7 +24996,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B878" s="2" t="n">
+      <c r="B878" s="1" t="n">
         <v>45452.82292824074</v>
       </c>
       <c r="C878" t="n">
@@ -25036,7 +25024,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B879" s="2" t="n">
+      <c r="B879" s="1" t="n">
         <v>45452.83334490741</v>
       </c>
       <c r="C879" t="n">
@@ -25064,7 +25052,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B880" s="2" t="n">
+      <c r="B880" s="1" t="n">
         <v>45452.84376157408</v>
       </c>
       <c r="C880" t="n">
@@ -25092,7 +25080,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B881" s="2" t="n">
+      <c r="B881" s="1" t="n">
         <v>45452.85417824074</v>
       </c>
       <c r="C881" t="n">
@@ -25120,7 +25108,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B882" s="2" t="n">
+      <c r="B882" s="1" t="n">
         <v>45452.86459490741</v>
       </c>
       <c r="C882" t="n">
@@ -25148,7 +25136,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B883" s="2" t="n">
+      <c r="B883" s="1" t="n">
         <v>45452.87501157408</v>
       </c>
       <c r="C883" t="n">
@@ -25176,7 +25164,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B884" s="2" t="n">
+      <c r="B884" s="1" t="n">
         <v>45452.88542824074</v>
       </c>
       <c r="C884" t="n">
@@ -25204,7 +25192,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B885" s="2" t="n">
+      <c r="B885" s="1" t="n">
         <v>45452.89585648148</v>
       </c>
       <c r="C885" t="n">
@@ -25232,7 +25220,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B886" s="2" t="n">
+      <c r="B886" s="1" t="n">
         <v>45452.90626157408</v>
       </c>
       <c r="C886" t="n">
@@ -25260,7 +25248,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B887" s="2" t="n">
+      <c r="B887" s="1" t="n">
         <v>45452.91668981482</v>
       </c>
       <c r="C887" t="n">
@@ -25288,7 +25276,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B888" s="2" t="n">
+      <c r="B888" s="1" t="n">
         <v>45452.92710648148</v>
       </c>
       <c r="C888" t="n">
@@ -25316,7 +25304,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B889" s="2" t="n">
+      <c r="B889" s="1" t="n">
         <v>45452.93752314815</v>
       </c>
       <c r="C889" t="n">
@@ -25344,7 +25332,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B890" s="2" t="n">
+      <c r="B890" s="1" t="n">
         <v>45452.94793981482</v>
       </c>
       <c r="C890" t="n">
@@ -25372,7 +25360,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B891" s="2" t="n">
+      <c r="B891" s="1" t="n">
         <v>45452.95834490741</v>
       </c>
       <c r="C891" t="n">
@@ -25400,7 +25388,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B892" s="2" t="n">
+      <c r="B892" s="1" t="n">
         <v>45452.96876157408</v>
       </c>
       <c r="C892" t="n">
@@ -25428,7 +25416,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B893" s="2" t="n">
+      <c r="B893" s="1" t="n">
         <v>45452.97917824074</v>
       </c>
       <c r="C893" t="n">
@@ -25456,7 +25444,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B894" s="2" t="n">
+      <c r="B894" s="1" t="n">
         <v>45452.98959490741</v>
       </c>
       <c r="C894" t="n">
@@ -25484,7 +25472,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B895" s="2" t="n">
+      <c r="B895" s="1" t="n">
         <v>45453.00002314815</v>
       </c>
       <c r="C895" t="n">
@@ -25512,7 +25500,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B896" s="2" t="n">
+      <c r="B896" s="1" t="n">
         <v>45453.01043981482</v>
       </c>
       <c r="C896" t="n">
@@ -25540,7 +25528,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B897" s="2" t="n">
+      <c r="B897" s="1" t="n">
         <v>45453.02085648148</v>
       </c>
       <c r="C897" t="n">
@@ -25568,7 +25556,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B898" s="2" t="n">
+      <c r="B898" s="1" t="n">
         <v>45453.03126157408</v>
       </c>
       <c r="C898" t="n">
@@ -25596,7 +25584,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B899" s="2" t="n">
+      <c r="B899" s="1" t="n">
         <v>45453.04167824074</v>
       </c>
       <c r="C899" t="n">
@@ -25624,7 +25612,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B900" s="2" t="n">
+      <c r="B900" s="1" t="n">
         <v>45453.05209490741</v>
       </c>
       <c r="C900" t="n">
@@ -25652,7 +25640,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B901" s="2" t="n">
+      <c r="B901" s="1" t="n">
         <v>45453.06251157408</v>
       </c>
       <c r="C901" t="n">
@@ -25680,7 +25668,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B902" s="2" t="n">
+      <c r="B902" s="1" t="n">
         <v>45453.07292824074</v>
       </c>
       <c r="C902" t="n">
@@ -25708,7 +25696,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B903" s="2" t="n">
+      <c r="B903" s="1" t="n">
         <v>45453.08335648148</v>
       </c>
       <c r="C903" t="n">
@@ -25736,7 +25724,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B904" s="2" t="n">
+      <c r="B904" s="1" t="n">
         <v>45453.09377314815</v>
       </c>
       <c r="C904" t="n">
@@ -25764,7 +25752,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B905" s="2" t="n">
+      <c r="B905" s="1" t="n">
         <v>45453.10417824074</v>
       </c>
       <c r="C905" t="n">
@@ -25792,7 +25780,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B906" s="2" t="n">
+      <c r="B906" s="1" t="n">
         <v>45453.11459490741</v>
       </c>
       <c r="C906" t="n">
@@ -25820,7 +25808,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B907" s="2" t="n">
+      <c r="B907" s="1" t="n">
         <v>45453.12501157408</v>
       </c>
       <c r="C907" t="n">
@@ -25848,7 +25836,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B908" s="2" t="n">
+      <c r="B908" s="1" t="n">
         <v>45453.13542824074</v>
       </c>
       <c r="C908" t="n">
@@ -25876,7 +25864,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B909" s="2" t="n">
+      <c r="B909" s="1" t="n">
         <v>45453.14585648148</v>
       </c>
       <c r="C909" t="n">
@@ -25904,7 +25892,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B910" s="2" t="n">
+      <c r="B910" s="1" t="n">
         <v>45453.15627314815</v>
       </c>
       <c r="C910" t="n">
@@ -25932,7 +25920,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B911" s="2" t="n">
+      <c r="B911" s="1" t="n">
         <v>45453.16668981482</v>
       </c>
       <c r="C911" t="n">
@@ -25960,7 +25948,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B912" s="2" t="n">
+      <c r="B912" s="1" t="n">
         <v>45453.17709490741</v>
       </c>
       <c r="C912" t="n">
@@ -25988,7 +25976,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B913" s="2" t="n">
+      <c r="B913" s="1" t="n">
         <v>45453.18751157408</v>
       </c>
       <c r="C913" t="n">
@@ -26016,7 +26004,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B914" s="2" t="n">
+      <c r="B914" s="1" t="n">
         <v>45453.19792824074</v>
       </c>
       <c r="C914" t="n">
@@ -26044,7 +26032,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B915" s="2" t="n">
+      <c r="B915" s="1" t="n">
         <v>45453.20835648148</v>
       </c>
       <c r="C915" t="n">
@@ -26072,7 +26060,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B916" s="2" t="n">
+      <c r="B916" s="1" t="n">
         <v>45453.21877314815</v>
       </c>
       <c r="C916" t="n">
@@ -26100,7 +26088,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B917" s="2" t="n">
+      <c r="B917" s="1" t="n">
         <v>45453.22917824074</v>
       </c>
       <c r="C917" t="n">
@@ -26128,7 +26116,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B918" s="2" t="n">
+      <c r="B918" s="1" t="n">
         <v>45453.23959490741</v>
       </c>
       <c r="C918" t="n">
@@ -26156,7 +26144,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B919" s="2" t="n">
+      <c r="B919" s="1" t="n">
         <v>45453.25001157408</v>
       </c>
       <c r="C919" t="n">
@@ -26184,7 +26172,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B920" s="2" t="n">
+      <c r="B920" s="1" t="n">
         <v>45453.26042824074</v>
       </c>
       <c r="C920" t="n">
@@ -26212,7 +26200,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B921" s="2" t="n">
+      <c r="B921" s="1" t="n">
         <v>45453.27084490741</v>
       </c>
       <c r="C921" t="n">
@@ -26240,7 +26228,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B922" s="2" t="n">
+      <c r="B922" s="1" t="n">
         <v>45453.28127314815</v>
       </c>
       <c r="C922" t="n">
@@ -26268,7 +26256,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B923" s="2" t="n">
+      <c r="B923" s="1" t="n">
         <v>45453.29168981482</v>
       </c>
       <c r="C923" t="n">
@@ -26296,7 +26284,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B924" s="2" t="n">
+      <c r="B924" s="1" t="n">
         <v>45453.30210648148</v>
       </c>
       <c r="C924" t="n">
@@ -26324,7 +26312,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B925" s="2" t="n">
+      <c r="B925" s="1" t="n">
         <v>45453.31252314815</v>
       </c>
       <c r="C925" t="n">
@@ -26352,7 +26340,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B926" s="2" t="n">
+      <c r="B926" s="1" t="n">
         <v>45453.32292824074</v>
       </c>
       <c r="C926" t="n">
@@ -26380,7 +26368,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B927" s="2" t="n">
+      <c r="B927" s="1" t="n">
         <v>45453.33334490741</v>
       </c>
       <c r="C927" t="n">
@@ -26408,7 +26396,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B928" s="2" t="n">
+      <c r="B928" s="1" t="n">
         <v>45453.34377314815</v>
       </c>
       <c r="C928" t="n">
@@ -26436,7 +26424,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B929" s="2" t="n">
+      <c r="B929" s="1" t="n">
         <v>45453.35417824074</v>
       </c>
       <c r="C929" t="n">
@@ -26464,7 +26452,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B930" s="2" t="n">
+      <c r="B930" s="1" t="n">
         <v>45453.36460648148</v>
       </c>
       <c r="C930" t="n">
@@ -26492,7 +26480,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B931" s="2" t="n">
+      <c r="B931" s="1" t="n">
         <v>45453.37502314815</v>
       </c>
       <c r="C931" t="n">
@@ -26520,7 +26508,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B932" s="2" t="n">
+      <c r="B932" s="1" t="n">
         <v>45453.38543981482</v>
       </c>
       <c r="C932" t="n">
@@ -26548,7 +26536,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B933" s="2" t="n">
+      <c r="B933" s="1" t="n">
         <v>45453.39585648148</v>
       </c>
       <c r="C933" t="n">
@@ -26576,7 +26564,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B934" s="2" t="n">
+      <c r="B934" s="1" t="n">
         <v>45453.40626157408</v>
       </c>
       <c r="C934" t="n">
@@ -26604,7 +26592,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B935" s="2" t="n">
+      <c r="B935" s="1" t="n">
         <v>45453.41667824074</v>
       </c>
       <c r="C935" t="n">
@@ -26632,7 +26620,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B936" s="2" t="n">
+      <c r="B936" s="1" t="n">
         <v>45453.42709490741</v>
       </c>
       <c r="C936" t="n">
@@ -26660,7 +26648,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B937" s="2" t="n">
+      <c r="B937" s="1" t="n">
         <v>45453.43752314815</v>
       </c>
       <c r="C937" t="n">
@@ -26688,7 +26676,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B938" s="2" t="n">
+      <c r="B938" s="1" t="n">
         <v>45453.44793981482</v>
       </c>
       <c r="C938" t="n">
@@ -26716,7 +26704,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B939" s="2" t="n">
+      <c r="B939" s="1" t="n">
         <v>45453.45834490741</v>
       </c>
       <c r="C939" t="n">
@@ -26744,7 +26732,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B940" s="2" t="n">
+      <c r="B940" s="1" t="n">
         <v>45453.46876157408</v>
       </c>
       <c r="C940" t="n">
@@ -26772,7 +26760,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B941" s="2" t="n">
+      <c r="B941" s="1" t="n">
         <v>45453.47917824074</v>
       </c>
       <c r="C941" t="n">
@@ -26800,7 +26788,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B942" s="2" t="n">
+      <c r="B942" s="1" t="n">
         <v>45453.48959490741</v>
       </c>
       <c r="C942" t="n">
@@ -26828,7 +26816,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B943" s="2" t="n">
+      <c r="B943" s="1" t="n">
         <v>45453.50002314815</v>
       </c>
       <c r="C943" t="n">
@@ -26856,7 +26844,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B944" s="2" t="n">
+      <c r="B944" s="1" t="n">
         <v>45453.51043981482</v>
       </c>
       <c r="C944" t="n">
@@ -26884,7 +26872,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B945" s="2" t="n">
+      <c r="B945" s="1" t="n">
         <v>45453.52085648148</v>
       </c>
       <c r="C945" t="n">
@@ -26912,7 +26900,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B946" s="2" t="n">
+      <c r="B946" s="1" t="n">
         <v>45453.53126157408</v>
       </c>
       <c r="C946" t="n">
@@ -26940,7 +26928,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B947" s="2" t="n">
+      <c r="B947" s="1" t="n">
         <v>45453.54167824074</v>
       </c>
       <c r="C947" t="n">
@@ -26968,7 +26956,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B948" s="2" t="n">
+      <c r="B948" s="1" t="n">
         <v>45453.55210648148</v>
       </c>
       <c r="C948" t="n">
@@ -26996,7 +26984,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B949" s="2" t="n">
+      <c r="B949" s="1" t="n">
         <v>45453.56251157408</v>
       </c>
       <c r="C949" t="n">
@@ -27024,7 +27012,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B950" s="2" t="n">
+      <c r="B950" s="1" t="n">
         <v>45453.57292824074</v>
       </c>
       <c r="C950" t="n">
@@ -27052,7 +27040,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B951" s="2" t="n">
+      <c r="B951" s="1" t="n">
         <v>45453.58335648148</v>
       </c>
       <c r="C951" t="n">
@@ -27080,7 +27068,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B952" s="2" t="n">
+      <c r="B952" s="1" t="n">
         <v>45453.59377314815</v>
       </c>
       <c r="C952" t="n">
@@ -27108,7 +27096,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B953" s="2" t="n">
+      <c r="B953" s="1" t="n">
         <v>45453.60418981482</v>
       </c>
       <c r="C953" t="n">
@@ -27136,7 +27124,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B954" s="2" t="n">
+      <c r="B954" s="1" t="n">
         <v>45453.61459490741</v>
       </c>
       <c r="C954" t="n">
@@ -27164,7 +27152,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B955" s="2" t="n">
+      <c r="B955" s="1" t="n">
         <v>45453.62501157408</v>
       </c>
       <c r="C955" t="n">
@@ -27192,7 +27180,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B956" s="2" t="n">
+      <c r="B956" s="1" t="n">
         <v>45453.63542824074</v>
       </c>
       <c r="C956" t="n">
@@ -27220,7 +27208,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B957" s="2" t="n">
+      <c r="B957" s="1" t="n">
         <v>45453.64584490741</v>
       </c>
       <c r="C957" t="n">
@@ -27248,7 +27236,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B958" s="2" t="n">
+      <c r="B958" s="1" t="n">
         <v>45453.65626157408</v>
       </c>
       <c r="C958" t="n">
@@ -27276,7 +27264,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B959" s="2" t="n">
+      <c r="B959" s="1" t="n">
         <v>45453.66668981482</v>
       </c>
       <c r="C959" t="n">
@@ -27304,7 +27292,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B960" s="2" t="n">
+      <c r="B960" s="1" t="n">
         <v>45453.67710648148</v>
       </c>
       <c r="C960" t="n">
@@ -27332,7 +27320,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B961" s="2" t="n">
+      <c r="B961" s="1" t="n">
         <v>45453.68751157408</v>
       </c>
       <c r="C961" t="n">
@@ -27360,7 +27348,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B962" s="2" t="n">
+      <c r="B962" s="1" t="n">
         <v>45453.69792824074</v>
       </c>
       <c r="C962" t="n">
@@ -27388,7 +27376,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B963" s="2" t="n">
+      <c r="B963" s="1" t="n">
         <v>45453.70834490741</v>
       </c>
       <c r="C963" t="n">
@@ -27416,7 +27404,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B964" s="2" t="n">
+      <c r="B964" s="1" t="n">
         <v>45453.71876157408</v>
       </c>
       <c r="C964" t="n">
@@ -27444,7 +27432,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B965" s="2" t="n">
+      <c r="B965" s="1" t="n">
         <v>45453.72917824074</v>
       </c>
       <c r="C965" t="n">
@@ -27472,7 +27460,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B966" s="2" t="n">
+      <c r="B966" s="1" t="n">
         <v>45453.73960648148</v>
       </c>
       <c r="C966" t="n">
@@ -27500,7 +27488,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B967" s="2" t="n">
+      <c r="B967" s="1" t="n">
         <v>45453.75002314815</v>
       </c>
       <c r="C967" t="n">
@@ -27528,7 +27516,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B968" s="2" t="n">
+      <c r="B968" s="1" t="n">
         <v>45453.76042824074</v>
       </c>
       <c r="C968" t="n">
@@ -27556,7 +27544,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B969" s="2" t="n">
+      <c r="B969" s="1" t="n">
         <v>45453.77084490741</v>
       </c>
       <c r="C969" t="n">
@@ -27584,7 +27572,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B970" s="2" t="n">
+      <c r="B970" s="1" t="n">
         <v>45453.78126157408</v>
       </c>
       <c r="C970" t="n">
@@ -27612,7 +27600,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B971" s="2" t="n">
+      <c r="B971" s="1" t="n">
         <v>45453.79167824074</v>
       </c>
       <c r="C971" t="n">
@@ -27640,7 +27628,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B972" s="2" t="n">
+      <c r="B972" s="1" t="n">
         <v>45453.80210648148</v>
       </c>
       <c r="C972" t="n">
@@ -27668,7 +27656,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B973" s="2" t="n">
+      <c r="B973" s="1" t="n">
         <v>45453.81252314815</v>
       </c>
       <c r="C973" t="n">
@@ -27696,7 +27684,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B974" s="2" t="n">
+      <c r="B974" s="1" t="n">
         <v>45453.82293981482</v>
       </c>
       <c r="C974" t="n">
@@ -27724,7 +27712,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B975" s="2" t="n">
+      <c r="B975" s="1" t="n">
         <v>45453.83334490741</v>
       </c>
       <c r="C975" t="n">
@@ -27752,7 +27740,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B976" s="2" t="n">
+      <c r="B976" s="1" t="n">
         <v>45453.84376157408</v>
       </c>
       <c r="C976" t="n">
@@ -27780,7 +27768,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B977" s="2" t="n">
+      <c r="B977" s="1" t="n">
         <v>45453.85417824074</v>
       </c>
       <c r="C977" t="n">
@@ -27808,7 +27796,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B978" s="2" t="n">
+      <c r="B978" s="1" t="n">
         <v>45453.86459490741</v>
       </c>
       <c r="C978" t="n">
@@ -27836,7 +27824,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B979" s="2" t="n">
+      <c r="B979" s="1" t="n">
         <v>45453.87502314815</v>
       </c>
       <c r="C979" t="n">
@@ -27864,7 +27852,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B980" s="2" t="n">
+      <c r="B980" s="1" t="n">
         <v>45453.88543981482</v>
       </c>
       <c r="C980" t="n">
@@ -27892,7 +27880,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B981" s="2" t="n">
+      <c r="B981" s="1" t="n">
         <v>45453.89585648148</v>
       </c>
       <c r="C981" t="n">
@@ -27920,7 +27908,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B982" s="2" t="n">
+      <c r="B982" s="1" t="n">
         <v>45453.90626157408</v>
       </c>
       <c r="C982" t="n">
@@ -27948,7 +27936,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B983" s="2" t="n">
+      <c r="B983" s="1" t="n">
         <v>45453.91667824074</v>
       </c>
       <c r="C983" t="n">
@@ -27976,7 +27964,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B984" s="2" t="n">
+      <c r="B984" s="1" t="n">
         <v>45453.92709490741</v>
       </c>
       <c r="C984" t="n">
@@ -28004,7 +27992,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B985" s="2" t="n">
+      <c r="B985" s="1" t="n">
         <v>45453.93751157408</v>
       </c>
       <c r="C985" t="n">
@@ -28032,7 +28020,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B986" s="2" t="n">
+      <c r="B986" s="1" t="n">
         <v>45453.94792824074</v>
       </c>
       <c r="C986" t="n">
@@ -28060,7 +28048,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B987" s="2" t="n">
+      <c r="B987" s="1" t="n">
         <v>45453.95835648148</v>
       </c>
       <c r="C987" t="n">
@@ -28088,7 +28076,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B988" s="2" t="n">
+      <c r="B988" s="1" t="n">
         <v>45453.96877314815</v>
       </c>
       <c r="C988" t="n">
@@ -28116,7 +28104,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B989" s="2" t="n">
+      <c r="B989" s="1" t="n">
         <v>45453.97917824074</v>
       </c>
       <c r="C989" t="n">
@@ -28144,7 +28132,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B990" s="2" t="n">
+      <c r="B990" s="1" t="n">
         <v>45453.98959490741</v>
       </c>
       <c r="C990" t="n">
@@ -28172,7 +28160,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B991" s="2" t="n">
+      <c r="B991" s="1" t="n">
         <v>45454.00001157408</v>
       </c>
       <c r="C991" t="n">
@@ -28200,7 +28188,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B992" s="2" t="n">
+      <c r="B992" s="1" t="n">
         <v>45454.01042824074</v>
       </c>
       <c r="C992" t="n">
@@ -28228,7 +28216,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B993" s="2" t="n">
+      <c r="B993" s="1" t="n">
         <v>45454.02084490741</v>
       </c>
       <c r="C993" t="n">
@@ -28256,7 +28244,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B994" s="2" t="n">
+      <c r="B994" s="1" t="n">
         <v>45454.03126157408</v>
       </c>
       <c r="C994" t="n">
@@ -28284,7 +28272,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B995" s="2" t="n">
+      <c r="B995" s="1" t="n">
         <v>45454.04167824074</v>
       </c>
       <c r="C995" t="n">
@@ -28312,7 +28300,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B996" s="2" t="n">
+      <c r="B996" s="1" t="n">
         <v>45454.05209490741</v>
       </c>
       <c r="C996" t="n">
@@ -28340,7 +28328,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B997" s="2" t="n">
+      <c r="B997" s="1" t="n">
         <v>45454.06251157408</v>
       </c>
       <c r="C997" t="n">
@@ -28368,7 +28356,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B998" s="2" t="n">
+      <c r="B998" s="1" t="n">
         <v>45454.07292824074</v>
       </c>
       <c r="C998" t="n">
@@ -28396,7 +28384,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B999" s="2" t="n">
+      <c r="B999" s="1" t="n">
         <v>45454.08334490741</v>
       </c>
       <c r="C999" t="n">
@@ -28424,7 +28412,7 @@
           <t>1wire_logger</t>
         </is>
       </c>
-      <c r="B1000" s="2" t="n">
+      <c r="B1000" s="1" t="n">
         <v>45454.09376157408</v>
       </c>
       <c r="C1000" t="n">
